--- a/scm_input_cleaned.xlsx
+++ b/scm_input_cleaned.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5611d695511771a1/Desktop/Repositories/scm_model/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="169" documentId="8_{69118542-9163-4E18-BF71-86AAA6BFC266}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EDEBB521-F453-4792-AA0F-06900662655F}"/>
+  <xr:revisionPtr revIDLastSave="190" documentId="8_{69118542-9163-4E18-BF71-86AAA6BFC266}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9AC96B1F-2C60-47AA-B1E8-F999E3D75D1F}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{D3628906-A666-41FC-B4DD-112A108B04C0}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="5" xr2:uid="{D3628906-A666-41FC-B4DD-112A108B04C0}"/>
   </bookViews>
   <sheets>
     <sheet name="timeseries" sheetId="1" r:id="rId1"/>
@@ -22,6 +22,7 @@
     <sheet name="economic_transport" sheetId="7" r:id="rId7"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">ng_flows!$B$1:$B$217</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">sink_blocks!$D$1:$D$60</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -1300,8 +1301,7 @@
         <v>2026</v>
       </c>
       <c r="B2" s="3">
-        <f>1/100</f>
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="C2">
         <v>202000</v>
@@ -5901,7 +5901,7 @@
         <v>129</v>
       </c>
       <c r="E2">
-        <v>43.900036572472978</v>
+        <v>91.346707935673805</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -6037,7 +6037,7 @@
         <v>129</v>
       </c>
       <c r="E10">
-        <v>48.467335167527011</v>
+        <v>100.8502920643262</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -6819,7 +6819,7 @@
         <v>128</v>
       </c>
       <c r="E56">
-        <v>51.33081286985923</v>
+        <v>32.492749807386559</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
@@ -6955,7 +6955,7 @@
         <v>128</v>
       </c>
       <c r="E64">
-        <v>56.671199070140773</v>
+        <v>35.873250192613433</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
@@ -7805,7 +7805,7 @@
         <v>131</v>
       </c>
       <c r="E114">
-        <v>0</v>
+        <v>0.78632377625652949</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.25">
@@ -7822,7 +7822,7 @@
         <v>131</v>
       </c>
       <c r="E115">
-        <v>0</v>
+        <v>9.4144333760472563</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.25">
@@ -7839,7 +7839,7 @@
         <v>131</v>
       </c>
       <c r="E116">
-        <v>0</v>
+        <v>1.1111111111111109</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.25">
@@ -7856,7 +7856,7 @@
         <v>131</v>
       </c>
       <c r="E117">
-        <v>0</v>
+        <v>26.946356145403541</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.25">
@@ -7958,7 +7958,7 @@
         <v>131</v>
       </c>
       <c r="E123">
-        <v>0</v>
+        <v>1.4844705073478279</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.25">
@@ -7975,7 +7975,7 @@
         <v>131</v>
       </c>
       <c r="E124">
-        <v>0</v>
+        <v>17.773147795004309</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.25">
@@ -7992,7 +7992,7 @@
         <v>131</v>
       </c>
       <c r="E125">
-        <v>0</v>
+        <v>2.2222222222222219</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.25">
@@ -8009,7 +8009,7 @@
         <v>131</v>
       </c>
       <c r="E126">
-        <v>0</v>
+        <v>50.870992568451292</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.25">
@@ -8111,7 +8111,7 @@
         <v>131</v>
       </c>
       <c r="E132">
-        <v>0</v>
+        <v>1.470180788882288</v>
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.25">
@@ -8128,7 +8128,7 @@
         <v>131</v>
       </c>
       <c r="E133">
-        <v>0</v>
+        <v>17.602061015590419</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.25">
@@ -8145,7 +8145,7 @@
         <v>131</v>
       </c>
       <c r="E134">
-        <v>0</v>
+        <v>3.333333333333333</v>
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.25">
@@ -8162,7 +8162,7 @@
         <v>131</v>
       </c>
       <c r="E135">
-        <v>0</v>
+        <v>50.381301356488777</v>
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.25">
@@ -8264,7 +8264,7 @@
         <v>131</v>
       </c>
       <c r="E141">
-        <v>0</v>
+        <v>0.89285945878639206</v>
       </c>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.25">
@@ -8281,7 +8281,7 @@
         <v>131</v>
       </c>
       <c r="E142">
-        <v>0</v>
+        <v>10.68995513392159</v>
       </c>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.25">
@@ -8298,7 +8298,7 @@
         <v>131</v>
       </c>
       <c r="E143">
-        <v>0</v>
+        <v>3.8888888888888888</v>
       </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.25">
@@ -8315,7 +8315,7 @@
         <v>131</v>
       </c>
       <c r="E144">
-        <v>0</v>
+        <v>30.597203964491701</v>
       </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.25">
@@ -8417,7 +8417,7 @@
         <v>131</v>
       </c>
       <c r="E150">
-        <v>0</v>
+        <v>0.43653689984869187</v>
       </c>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.25">
@@ -8434,7 +8434,7 @@
         <v>131</v>
       </c>
       <c r="E151">
-        <v>0</v>
+        <v>5.2265335017301622</v>
       </c>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.25">
@@ -8451,7 +8451,7 @@
         <v>131</v>
       </c>
       <c r="E152">
-        <v>0</v>
+        <v>3.6111111111111112</v>
       </c>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.25">
@@ -8468,7 +8468,7 @@
         <v>131</v>
       </c>
       <c r="E153">
-        <v>0</v>
+        <v>14.95958678743504</v>
       </c>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.25">
@@ -8570,7 +8570,7 @@
         <v>131</v>
       </c>
       <c r="E159">
-        <v>0</v>
+        <v>0.26866807811826832</v>
       </c>
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.25">
@@ -8587,7 +8587,7 @@
         <v>131</v>
       </c>
       <c r="E160">
-        <v>0</v>
+        <v>3.2166873215466931</v>
       </c>
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.25">
@@ -8604,7 +8604,7 @@
         <v>131</v>
       </c>
       <c r="E161">
-        <v>0</v>
+        <v>3.333333333333333</v>
       </c>
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.25">
@@ -8621,7 +8621,7 @@
         <v>131</v>
       </c>
       <c r="E162">
-        <v>0</v>
+        <v>9.2069271418216783</v>
       </c>
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.25">
@@ -8655,7 +8655,7 @@
         <v>132</v>
       </c>
       <c r="E164">
-        <v>186.05626926236491</v>
+        <v>164.75172986911201</v>
       </c>
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.25">
@@ -8723,7 +8723,7 @@
         <v>132</v>
       </c>
       <c r="E168">
-        <v>25.647718742141141</v>
+        <v>24.141085746979751</v>
       </c>
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.25">
@@ -8740,7 +8740,7 @@
         <v>132</v>
       </c>
       <c r="E169">
-        <v>307.07292165957989</v>
+        <v>289.03442863240991</v>
       </c>
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.25">
@@ -8774,7 +8774,7 @@
         <v>132</v>
       </c>
       <c r="E171">
-        <v>878.91601959827881</v>
+        <v>827.28554562061026</v>
       </c>
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.25">
@@ -8791,7 +8791,7 @@
         <v>132</v>
       </c>
       <c r="E172">
-        <v>205.41330409763509</v>
+        <v>181.89227013088811</v>
       </c>
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.25">
@@ -8876,7 +8876,7 @@
         <v>132</v>
       </c>
       <c r="E177">
-        <v>14.544178222408441</v>
+        <v>13.82385009432965</v>
       </c>
     </row>
     <row r="178" spans="1:5" x14ac:dyDescent="0.25">
@@ -8893,7 +8893,7 @@
         <v>132</v>
       </c>
       <c r="E178">
-        <v>174.13335450199</v>
+        <v>165.5090684566469</v>
       </c>
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.25">
@@ -8927,7 +8927,7 @@
         <v>132</v>
       </c>
       <c r="E180">
-        <v>498.41123727560148</v>
+        <v>473.72647144902339</v>
       </c>
     </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.25">
@@ -9029,7 +9029,7 @@
         <v>132</v>
       </c>
       <c r="E186">
-        <v>6.0238239801640558</v>
+        <v>5.6688297352257022</v>
       </c>
     </row>
     <row r="187" spans="1:5" x14ac:dyDescent="0.25">
@@ -9046,7 +9046,7 @@
         <v>132</v>
       </c>
       <c r="E187">
-        <v>72.121549980690148</v>
+        <v>67.871303747817734</v>
       </c>
     </row>
     <row r="188" spans="1:5" x14ac:dyDescent="0.25">
@@ -9080,7 +9080,7 @@
         <v>132</v>
       </c>
       <c r="E189">
-        <v>206.4290960391458</v>
+        <v>194.2638765169566</v>
       </c>
     </row>
     <row r="190" spans="1:5" x14ac:dyDescent="0.25">
@@ -9182,7 +9182,7 @@
         <v>132</v>
       </c>
       <c r="E195">
-        <v>1.8493181470020179</v>
+        <v>1.6380941094450781</v>
       </c>
     </row>
     <row r="196" spans="1:5" x14ac:dyDescent="0.25">
@@ -9199,7 +9199,7 @@
         <v>132</v>
       </c>
       <c r="E196">
-        <v>22.141365950996949</v>
+        <v>19.612439967776059</v>
       </c>
     </row>
     <row r="197" spans="1:5" x14ac:dyDescent="0.25">
@@ -9233,7 +9233,7 @@
         <v>132</v>
       </c>
       <c r="E198">
-        <v>63.373875902001018</v>
+        <v>56.135485922778869</v>
       </c>
     </row>
     <row r="199" spans="1:5" x14ac:dyDescent="0.25">
@@ -9335,7 +9335,7 @@
         <v>132</v>
       </c>
       <c r="E204">
-        <v>2.1176563765323961</v>
+        <v>1.9202185232449069</v>
       </c>
     </row>
     <row r="205" spans="1:5" x14ac:dyDescent="0.25">
@@ -9352,7 +9352,7 @@
         <v>132</v>
       </c>
       <c r="E205">
-        <v>25.354104088189001</v>
+        <v>22.99023621109907</v>
       </c>
     </row>
     <row r="206" spans="1:5" x14ac:dyDescent="0.25">
@@ -9386,7 +9386,7 @@
         <v>132</v>
       </c>
       <c r="E207">
-        <v>72.569499535278595</v>
+        <v>65.803545265656012</v>
       </c>
     </row>
     <row r="208" spans="1:5" x14ac:dyDescent="0.25">
@@ -9488,7 +9488,7 @@
         <v>132</v>
       </c>
       <c r="E213">
-        <v>2.1097785569498528</v>
+        <v>1.945821436888173</v>
       </c>
     </row>
     <row r="214" spans="1:5" x14ac:dyDescent="0.25">
@@ -9505,7 +9505,7 @@
         <v>132</v>
       </c>
       <c r="E214">
-        <v>25.25978517039988</v>
+        <v>23.29677269391372</v>
       </c>
     </row>
     <row r="215" spans="1:5" x14ac:dyDescent="0.25">
@@ -9539,7 +9539,7 @@
         <v>132</v>
       </c>
       <c r="E216">
-        <v>72.299536272650272</v>
+        <v>66.680925869198092</v>
       </c>
     </row>
     <row r="217" spans="1:5" x14ac:dyDescent="0.25">
@@ -9560,6 +9560,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="B1:B217" xr:uid="{1F3C079C-E0FE-4643-9E48-5AE3F12A3520}"/>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
@@ -9655,7 +9656,7 @@
         <v>40</v>
       </c>
       <c r="C8">
-        <v>100</v>
+        <v>818</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -9666,7 +9667,7 @@
         <v>31</v>
       </c>
       <c r="C9">
-        <v>100</v>
+        <v>781</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -9677,7 +9678,7 @@
         <v>32</v>
       </c>
       <c r="C10">
-        <v>100</v>
+        <v>297</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -9723,13 +9724,13 @@
         <v>122</v>
       </c>
       <c r="B2">
-        <v>6.2E-2</v>
+        <v>31</v>
       </c>
       <c r="C2">
-        <v>7.8E-2</v>
+        <v>39</v>
       </c>
       <c r="D2">
-        <v>7.0000000000000007E-2</v>
+        <v>35</v>
       </c>
       <c r="E2">
         <v>0.9</v>
@@ -9740,13 +9741,13 @@
         <v>123</v>
       </c>
       <c r="B3">
-        <v>3.1E-2</v>
+        <v>31</v>
       </c>
       <c r="C3">
-        <v>3.7999999999999999E-2</v>
+        <v>38</v>
       </c>
       <c r="D3">
-        <v>3.4500000000000003E-2</v>
+        <v>35</v>
       </c>
       <c r="E3">
         <v>0.9</v>

--- a/scm_input_cleaned.xlsx
+++ b/scm_input_cleaned.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5611d695511771a1/Desktop/Repositories/scm_model/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="190" documentId="8_{69118542-9163-4E18-BF71-86AAA6BFC266}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9AC96B1F-2C60-47AA-B1E8-F999E3D75D1F}"/>
+  <xr:revisionPtr revIDLastSave="218" documentId="8_{69118542-9163-4E18-BF71-86AAA6BFC266}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{50965CE7-4362-4F8C-8802-6DEF5AFEF792}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="5" xr2:uid="{D3628906-A666-41FC-B4DD-112A108B04C0}"/>
+    <workbookView xWindow="-28920" yWindow="6825" windowWidth="29040" windowHeight="17520" xr2:uid="{D3628906-A666-41FC-B4DD-112A108B04C0}"/>
   </bookViews>
   <sheets>
     <sheet name="timeseries" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
     <sheet name="economic_transport" sheetId="7" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">ng_flows!$B$1:$B$217</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">ng_flows!$D$1:$D$217</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">sink_blocks!$D$1:$D$60</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -250,7 +250,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1002" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1017" uniqueCount="156">
   <si>
     <t>year</t>
   </si>
@@ -321,9 +321,6 @@
     <t>rho_power</t>
   </si>
   <si>
-    <t>rho_industry</t>
-  </si>
-  <si>
     <t>Lineare Interpolation, sector gewichteter prozentsatz.</t>
   </si>
   <si>
@@ -712,6 +709,15 @@
   </si>
   <si>
     <t>Industry_refining</t>
+  </si>
+  <si>
+    <t>rho_otherindustries</t>
+  </si>
+  <si>
+    <t>Industry_other</t>
+  </si>
+  <si>
+    <t>psc_otherindustry</t>
   </si>
 </sst>
 </file>
@@ -1281,19 +1287,19 @@
         <v>22</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>23</v>
+        <v>153</v>
       </c>
       <c r="K1" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>104</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
@@ -2495,7 +2501,7 @@
         <v>18</v>
       </c>
       <c r="J28" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
@@ -2533,57 +2539,57 @@
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>30</v>
-      </c>
       <c r="G1" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>134</v>
-      </c>
       <c r="L1" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="M1" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>97</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D2" s="10">
         <f>2027-2026</f>
@@ -2622,13 +2628,13 @@
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D3" s="10">
         <f>2030-2026</f>
@@ -2667,13 +2673,13 @@
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D4" s="10">
         <f>2028-2026</f>
@@ -2712,13 +2718,13 @@
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D5" s="10">
         <f>2035-2026</f>
@@ -2757,13 +2763,13 @@
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D6" s="10">
         <f>2027-2026</f>
@@ -2802,13 +2808,13 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D7" s="10">
         <f>2030-2026</f>
@@ -2847,13 +2853,13 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D8" s="10">
         <f>2035-2026</f>
@@ -2892,13 +2898,13 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D9" s="10">
         <f>2032-2026</f>
@@ -2937,13 +2943,13 @@
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D10" s="10">
         <f>2030-2026</f>
@@ -2982,13 +2988,13 @@
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D11" s="10">
         <f>2029-2026</f>
@@ -3027,13 +3033,13 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D12" s="10">
         <f>2034-2026</f>
@@ -3072,13 +3078,13 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D13" s="10">
         <f>2040-2026</f>
@@ -3117,13 +3123,13 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D14" s="10">
         <f>2031-2026</f>
@@ -3162,13 +3168,13 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D15" s="10">
         <v>8</v>
@@ -3206,13 +3212,13 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D16" s="10">
         <f>2029-2026</f>
@@ -3251,13 +3257,13 @@
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C17" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D17" s="10">
         <f>2034-2026</f>
@@ -3296,13 +3302,13 @@
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D18" s="10">
         <f>2026-2026</f>
@@ -3341,13 +3347,13 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C19" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D19" s="10">
         <f>2030-2026</f>
@@ -3386,13 +3392,13 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D20" s="10">
         <f>2030-2026</f>
@@ -3431,13 +3437,13 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D21" s="10">
         <f>2033-2026</f>
@@ -3476,13 +3482,13 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D22" s="10">
         <f>2028-2026</f>
@@ -3521,13 +3527,13 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C23" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D23" s="10">
         <f>2030-2026</f>
@@ -3566,13 +3572,13 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C24" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D24" s="10">
         <f>2027-2026</f>
@@ -3611,13 +3617,13 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C25" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D25" s="10">
         <f>2030-2026</f>
@@ -3656,13 +3662,13 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C26" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D26" s="10">
         <f>2030-2026</f>
@@ -3701,13 +3707,13 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C27" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D27" s="10">
         <f>2030-2026</f>
@@ -3746,13 +3752,13 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C28" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D28" s="10">
         <v>0</v>
@@ -3790,13 +3796,13 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C29" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D29" s="10">
         <f>2030-2026</f>
@@ -3835,13 +3841,13 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C30" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D30" s="10">
         <f>2028-2026</f>
@@ -3880,13 +3886,13 @@
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C31" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D31" s="10">
         <f>2030-2026</f>
@@ -3925,13 +3931,13 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D32" s="10">
         <f>2027-2026</f>
@@ -3970,13 +3976,13 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D33" s="10">
         <f>2037-2026</f>
@@ -4015,13 +4021,13 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D34" s="10">
         <v>0</v>
@@ -4059,13 +4065,13 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D35" s="10">
         <f>2028-2026</f>
@@ -4104,13 +4110,13 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D36" s="10">
         <f>2032-2026</f>
@@ -4149,13 +4155,13 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D37" s="10">
         <f>2034-2026</f>
@@ -4194,13 +4200,13 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D38" s="10">
         <f>2029-2026</f>
@@ -4239,13 +4245,13 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D39" s="10">
         <v>3</v>
@@ -4283,13 +4289,13 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C40" s="9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D40" s="10">
         <f>2030-2026</f>
@@ -4328,13 +4334,13 @@
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D41" s="10">
         <f>2033-2026</f>
@@ -4373,13 +4379,13 @@
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D42" s="10">
         <f>2033-2026</f>
@@ -4418,13 +4424,13 @@
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C43" s="9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D43" s="10">
         <f>2030-2026</f>
@@ -4463,13 +4469,13 @@
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C44" s="9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D44" s="10">
         <v>8</v>
@@ -4507,13 +4513,13 @@
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C45" s="9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D45" s="10">
         <f>2028-2026</f>
@@ -4552,13 +4558,13 @@
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C46" s="9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D46" s="10">
         <f>2035-2026</f>
@@ -4597,13 +4603,13 @@
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A47" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="B47" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="C47" t="s">
         <v>40</v>
-      </c>
-      <c r="B47" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="C47" t="s">
-        <v>41</v>
       </c>
       <c r="D47" s="10">
         <f>2030-2026</f>
@@ -4642,13 +4648,13 @@
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A48" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="B48" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="C48" t="s">
         <v>40</v>
-      </c>
-      <c r="B48" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="C48" t="s">
-        <v>41</v>
       </c>
       <c r="D48" s="10">
         <f>2029-2026</f>
@@ -4687,13 +4693,13 @@
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A49" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="B49" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="C49" t="s">
         <v>40</v>
-      </c>
-      <c r="B49" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="C49" t="s">
-        <v>41</v>
       </c>
       <c r="D49" s="10">
         <f>2031-2026</f>
@@ -4732,13 +4738,13 @@
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A50" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="B50" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="C50" t="s">
         <v>40</v>
-      </c>
-      <c r="B50" s="9" t="s">
-        <v>130</v>
-      </c>
-      <c r="C50" t="s">
-        <v>41</v>
       </c>
       <c r="D50" s="10">
         <f>2031-2026</f>
@@ -4777,13 +4783,13 @@
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A51" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B51" s="9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C51" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D51">
         <f>2032-2026</f>
@@ -4822,13 +4828,13 @@
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A52" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B52" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C52" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D52" s="10">
         <f>2029-2026</f>
@@ -4867,13 +4873,13 @@
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A53" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B53" s="9" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C53" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D53" s="10">
         <f>2029-2026</f>
@@ -4912,13 +4918,13 @@
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A54" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B54" s="9" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C54" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D54">
         <f>2034-2026</f>
@@ -4957,13 +4963,13 @@
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A55" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B55" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C55" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D55" s="10">
         <f>2030-2026</f>
@@ -5002,13 +5008,13 @@
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A56" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B56" s="9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C56" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D56" s="10">
         <v>8</v>
@@ -5046,13 +5052,13 @@
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A57" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B57" s="9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C57" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D57" s="10">
         <f>2031-2026</f>
@@ -5091,13 +5097,13 @@
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A58" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B58" s="9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C58" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D58" s="10">
         <f>2029-2026</f>
@@ -5136,13 +5142,13 @@
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A59" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B59" s="9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C59" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D59">
         <f>2027-2026</f>
@@ -5181,13 +5187,13 @@
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A60" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B60" s="9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C60" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D60">
         <f>2028-2026</f>
@@ -5234,7 +5240,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62ABFD33-60F4-49E4-A8F6-CF75D47BDD76}">
-  <dimension ref="A1:N6"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -5242,57 +5248,57 @@
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>107</v>
-      </c>
       <c r="D1" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>134</v>
-      </c>
       <c r="I1" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="K1" s="1" t="s">
-        <v>98</v>
-      </c>
       <c r="L1" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="M1" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>110</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D2" s="7">
         <v>143</v>
@@ -5334,13 +5340,13 @@
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D3" s="7">
         <v>105</v>
@@ -5382,13 +5388,13 @@
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D4" s="7">
         <v>36</v>
@@ -5430,13 +5436,13 @@
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D5" s="7">
         <v>105</v>
@@ -5478,13 +5484,13 @@
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D6" s="7">
         <v>85</v>
@@ -5525,6 +5531,54 @@
       </c>
       <c r="N6">
         <v>90</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>154</v>
+      </c>
+      <c r="B7" t="s">
+        <v>155</v>
+      </c>
+      <c r="C7" t="s">
+        <v>107</v>
+      </c>
+      <c r="D7" s="7">
+        <v>143</v>
+      </c>
+      <c r="E7" s="7">
+        <v>131</v>
+      </c>
+      <c r="F7" s="7">
+        <v>111</v>
+      </c>
+      <c r="G7" s="7">
+        <v>95</v>
+      </c>
+      <c r="H7" s="7">
+        <f t="shared" ref="H7" si="1">D7*0.06</f>
+        <v>8.58</v>
+      </c>
+      <c r="I7" s="7">
+        <f t="shared" ref="I7" si="2">E7*0.06</f>
+        <v>7.8599999999999994</v>
+      </c>
+      <c r="J7" s="7">
+        <f t="shared" ref="J7" si="3">F7*0.06</f>
+        <v>6.66</v>
+      </c>
+      <c r="K7" s="7">
+        <f t="shared" ref="K7" si="4">G7*0.06</f>
+        <v>5.7</v>
+      </c>
+      <c r="L7" s="7">
+        <v>65</v>
+      </c>
+      <c r="M7" s="7">
+        <v>90</v>
+      </c>
+      <c r="N7">
+        <v>77.5</v>
       </c>
     </row>
   </sheetData>
@@ -5535,44 +5589,44 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{883056E3-C0AC-4D2F-A746-7D2A27055AB0}">
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B1" t="s">
+        <v>135</v>
+      </c>
+      <c r="C1" t="s">
+        <v>105</v>
+      </c>
+      <c r="D1" t="s">
         <v>136</v>
       </c>
-      <c r="C1" t="s">
-        <v>106</v>
-      </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>137</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>138</v>
-      </c>
-      <c r="F1" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F2">
         <v>0.8</v>
@@ -5580,19 +5634,19 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F3">
         <v>1</v>
@@ -5600,19 +5654,19 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D4">
         <v>0</v>
       </c>
       <c r="E4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F4">
         <v>0.75</v>
@@ -5620,19 +5674,19 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B5" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D5">
         <v>160000</v>
       </c>
       <c r="E5" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F5">
         <v>0.5</v>
@@ -5640,19 +5694,19 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D6">
         <v>100000</v>
       </c>
       <c r="E6" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F6">
         <v>1.5</v>
@@ -5660,19 +5714,19 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B7" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C7" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D7">
         <v>400000</v>
       </c>
       <c r="E7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F7">
         <v>0.4</v>
@@ -5680,19 +5734,19 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B8" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C8" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D8">
         <v>0</v>
       </c>
       <c r="E8" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F8">
         <v>0.5</v>
@@ -5700,19 +5754,19 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B9" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C9" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D9">
         <v>0</v>
       </c>
       <c r="E9" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F9">
         <v>0.5</v>
@@ -5720,19 +5774,19 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C10" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D10">
         <v>1700000</v>
       </c>
       <c r="E10" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F10">
         <v>0.3</v>
@@ -5740,19 +5794,19 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B11" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C11" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D11">
         <v>0</v>
       </c>
       <c r="E11" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F11">
         <v>0.6</v>
@@ -5760,19 +5814,19 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C12" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D12">
         <v>0</v>
       </c>
       <c r="E12" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F12">
         <v>0.8</v>
@@ -5780,19 +5834,19 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B13" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C13" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D13">
         <v>0</v>
       </c>
       <c r="E13" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F13">
         <v>1</v>
@@ -5800,19 +5854,19 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B14" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C14" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D14">
         <v>0</v>
       </c>
       <c r="E14" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F14">
         <v>1</v>
@@ -5820,19 +5874,19 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B15" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C15" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D15">
         <v>0</v>
       </c>
       <c r="E15" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F15">
         <v>0.9</v>
@@ -5840,22 +5894,82 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B16" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C16" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D16">
         <v>0</v>
       </c>
       <c r="E16" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F16">
         <v>1.2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>39</v>
+      </c>
+      <c r="B17" t="s">
+        <v>154</v>
+      </c>
+      <c r="C17" t="s">
+        <v>155</v>
+      </c>
+      <c r="D17">
+        <v>0</v>
+      </c>
+      <c r="E17" t="s">
+        <v>146</v>
+      </c>
+      <c r="F17">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>30</v>
+      </c>
+      <c r="B18" t="s">
+        <v>154</v>
+      </c>
+      <c r="C18" t="s">
+        <v>155</v>
+      </c>
+      <c r="D18">
+        <v>0</v>
+      </c>
+      <c r="E18" t="s">
+        <v>145</v>
+      </c>
+      <c r="F18">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>31</v>
+      </c>
+      <c r="B19" t="s">
+        <v>154</v>
+      </c>
+      <c r="C19" t="s">
+        <v>155</v>
+      </c>
+      <c r="D19">
+        <v>0</v>
+      </c>
+      <c r="E19" t="s">
+        <v>146</v>
+      </c>
+      <c r="F19">
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>
@@ -5867,6 +5981,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F3C079C-E0FE-4643-9E48-5AE3F12A3520}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:E217"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -5875,931 +5990,931 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>2026</v>
       </c>
       <c r="B2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E2">
         <v>91.346707935673805</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2026</v>
       </c>
       <c r="B3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2026</v>
       </c>
       <c r="B4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>2026</v>
       </c>
       <c r="B5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>2026</v>
       </c>
       <c r="B6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E6">
         <v>11.812967958185389</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>2026</v>
       </c>
       <c r="B7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E7">
         <v>141.4333423124618</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>2026</v>
       </c>
       <c r="B8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D8" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E8">
         <v>2.67</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>2026</v>
       </c>
       <c r="B9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D9" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E9">
         <v>404.81599481948882</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>2026</v>
       </c>
       <c r="B10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D10" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E10">
         <v>100.8502920643262</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>2030</v>
       </c>
       <c r="B11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D11" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E11">
         <v>28.073099119979691</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>2030</v>
       </c>
       <c r="B12" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D12" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E12">
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>2030</v>
       </c>
       <c r="B13" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D13" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E13">
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>2030</v>
       </c>
       <c r="B14" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C14" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D14" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E14">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>2030</v>
       </c>
       <c r="B15" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C15" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D15" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E15">
         <v>9.8816510339669801</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>2030</v>
       </c>
       <c r="B16" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C16" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D16" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E16">
         <v>118.31022806854629</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>2030</v>
       </c>
       <c r="B17" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C17" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D17" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E17">
         <v>2.14</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>2030</v>
       </c>
       <c r="B18" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C18" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D18" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E18">
         <v>338.63212089748669</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>2030</v>
       </c>
       <c r="B19" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C19" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D19" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E19">
         <v>30.993785210020299</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>2035</v>
       </c>
       <c r="B20" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C20" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D20" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E20">
         <v>27.939162342756621</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>2035</v>
       </c>
       <c r="B21" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C21" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D21" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E21">
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>2035</v>
       </c>
       <c r="B22" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C22" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D22" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E22">
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>2035</v>
       </c>
       <c r="B23" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C23" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D23" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E23">
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>2035</v>
       </c>
       <c r="B24" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C24" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D24" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E24">
         <v>6.951367170491487</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>2035</v>
       </c>
       <c r="B25" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C25" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D25" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E25">
         <v>83.226763675633933</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>2035</v>
       </c>
       <c r="B26" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C26" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D26" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E26">
         <v>1.6</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>2035</v>
       </c>
       <c r="B27" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C27" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D27" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E27">
         <v>238.2148691538745</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>2035</v>
       </c>
       <c r="B28" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C28" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D28" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E28">
         <v>30.845913837243369</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="12">
         <v>2040</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D29" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E29">
         <v>47.013994948645028</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="12">
         <v>2040</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D30" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E30">
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="12">
         <v>2040</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C31" s="12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D31" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E31">
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="12">
         <v>2040</v>
       </c>
       <c r="B32" s="12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C32" s="12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D32" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E32">
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="12">
         <v>2040</v>
       </c>
       <c r="B33" s="12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C33" s="12" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D33" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E33">
         <v>5.3565405287568293</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="12">
         <v>2040</v>
       </c>
       <c r="B34" s="12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C34" s="12" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D34" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E34">
         <v>64.132352927385313</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="12">
         <v>2040</v>
       </c>
       <c r="B35" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C35" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D35" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E35">
         <v>1.07</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="12">
         <v>2040</v>
       </c>
       <c r="B36" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C36" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D36" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E36">
         <v>183.56210654385791</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="12">
         <v>2040</v>
       </c>
       <c r="B37" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C37" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D37" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E37">
         <v>51.90526543135497</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="12">
         <v>2045</v>
       </c>
       <c r="B38" s="12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C38" s="12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D38" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E38">
         <v>50.179985896702192</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="12">
         <v>2045</v>
       </c>
       <c r="B39" s="12" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C39" s="12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D39" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E39">
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="12">
         <v>2045</v>
       </c>
       <c r="B40" s="12" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C40" s="12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D40" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E40">
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" s="12">
         <v>2045</v>
       </c>
       <c r="B41" s="12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C41" s="12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D41" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E41">
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" s="12">
         <v>2045</v>
       </c>
       <c r="B42" s="12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C42" s="12" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D42" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E42">
         <v>4.1055641162215259</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" s="12">
         <v>2045</v>
       </c>
       <c r="B43" s="12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C43" s="12" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D43" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E43">
         <v>49.154764246437132</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" s="12">
         <v>2045</v>
       </c>
       <c r="B44" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C44" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D44" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E44">
         <v>0.53</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" s="12">
         <v>2045</v>
       </c>
       <c r="B45" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C45" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D45" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E45">
         <v>140.69267163734131</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" s="12">
         <v>2045</v>
       </c>
       <c r="B46" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C46" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D46" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E46">
         <v>55.400641663297797</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" s="12">
         <v>2050</v>
       </c>
       <c r="B47" s="12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C47" s="12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D47" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E47">
         <v>47.501061705512093</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" s="12">
         <v>2050</v>
       </c>
       <c r="B48" s="12" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C48" s="12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D48" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E48">
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" s="12">
         <v>2050</v>
       </c>
       <c r="B49" s="12" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C49" s="12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D49" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E49">
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" s="12">
         <v>2050</v>
       </c>
       <c r="B50" s="12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C50" s="12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D50" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E50">
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" s="12">
         <v>2050</v>
       </c>
       <c r="B51" s="12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C51" s="12" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D51" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E51">
         <v>3.905083599061522</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" s="12">
         <v>2050</v>
       </c>
       <c r="B52" s="12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C52" s="12" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D52" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E52">
         <v>46.754467410719172</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" s="12">
         <v>2050</v>
       </c>
       <c r="B53" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C53" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D53" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E53">
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" s="12">
         <v>2050</v>
       </c>
       <c r="B54" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C54" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D54" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E54">
         <v>133.8224489902193</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" s="12">
         <v>2050</v>
       </c>
       <c r="B55" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C55" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D55" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E55">
         <v>52.443005934487907</v>
@@ -6810,13 +6925,13 @@
         <v>2026</v>
       </c>
       <c r="B56" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C56" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D56" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E56">
         <v>32.492749807386559</v>
@@ -6827,13 +6942,13 @@
         <v>2026</v>
       </c>
       <c r="B57" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C57" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D57" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E57">
         <v>0</v>
@@ -6844,13 +6959,13 @@
         <v>2026</v>
       </c>
       <c r="B58" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C58" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D58" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E58">
         <v>0</v>
@@ -6861,13 +6976,13 @@
         <v>2026</v>
       </c>
       <c r="B59" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C59" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D59" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E59">
         <v>0</v>
@@ -6878,13 +6993,13 @@
         <v>2026</v>
       </c>
       <c r="B60" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C60" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D60" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E60">
         <v>18.717144561125838</v>
@@ -6895,13 +7010,13 @@
         <v>2026</v>
       </c>
       <c r="B61" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C61" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D61" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E61">
         <v>224.09510659776549</v>
@@ -6912,13 +7027,13 @@
         <v>2026</v>
       </c>
       <c r="B62" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C62" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D62" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E62">
         <v>7.7777777777777777</v>
@@ -6929,13 +7044,13 @@
         <v>2026</v>
       </c>
       <c r="B63" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C63" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D63" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E63">
         <v>641.41370081700052</v>
@@ -6946,13 +7061,13 @@
         <v>2026</v>
       </c>
       <c r="B64" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C64" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D64" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E64">
         <v>35.873250192613433</v>
@@ -6963,13 +7078,13 @@
         <v>2030</v>
       </c>
       <c r="B65" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C65" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D65" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E65">
         <v>39.832212400033853</v>
@@ -6980,13 +7095,13 @@
         <v>2030</v>
       </c>
       <c r="B66" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C66" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D66" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E66">
         <v>0</v>
@@ -6997,13 +7112,13 @@
         <v>2030</v>
       </c>
       <c r="B67" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C67" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D67" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E67">
         <v>0</v>
@@ -7014,13 +7129,13 @@
         <v>2030</v>
       </c>
       <c r="B68" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C68" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D68" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E68">
         <v>0</v>
@@ -7031,13 +7146,13 @@
         <v>2030</v>
       </c>
       <c r="B69" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C69" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D69" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E69">
         <v>14.610653842703581</v>
@@ -7048,13 +7163,13 @@
         <v>2030</v>
       </c>
       <c r="B70" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C70" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D70" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E70">
         <v>174.92924840383711</v>
@@ -7065,13 +7180,13 @@
         <v>2030</v>
       </c>
       <c r="B71" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C71" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D71" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E71">
         <v>5.9722222222222223</v>
@@ -7082,13 +7197,13 @@
         <v>2030</v>
       </c>
       <c r="B72" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C72" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D72" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E72">
         <v>500.68927565310952</v>
@@ -7099,13 +7214,13 @@
         <v>2030</v>
       </c>
       <c r="B73" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C73" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D73" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E73">
         <v>43.97630023996615</v>
@@ -7116,13 +7231,13 @@
         <v>2035</v>
       </c>
       <c r="B74" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C74" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D74" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E74">
         <v>23.706679694440709</v>
@@ -7133,13 +7248,13 @@
         <v>2035</v>
       </c>
       <c r="B75" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C75" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D75" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E75">
         <v>0</v>
@@ -7150,13 +7265,13 @@
         <v>2035</v>
       </c>
       <c r="B76" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C76" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D76" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E76">
         <v>0</v>
@@ -7167,13 +7282,13 @@
         <v>2035</v>
       </c>
       <c r="B77" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C77" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D77" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E77">
         <v>0</v>
@@ -7184,13 +7299,13 @@
         <v>2035</v>
       </c>
       <c r="B78" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C78" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D78" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E78">
         <v>10.90299599509941</v>
@@ -7201,13 +7316,13 @@
         <v>2035</v>
       </c>
       <c r="B79" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C79" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D79" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E79">
         <v>130.53850397839989</v>
@@ -7218,13 +7333,13 @@
         <v>2035</v>
       </c>
       <c r="B80" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C80" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D80" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E80">
         <v>4.166666666666667</v>
@@ -7235,13 +7350,13 @@
         <v>2035</v>
       </c>
       <c r="B81" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C81" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D81" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E81">
         <v>373.63236621756351</v>
@@ -7252,13 +7367,13 @@
         <v>2035</v>
       </c>
       <c r="B82" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C82" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D82" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E82">
         <v>26.17308959555929</v>
@@ -7269,13 +7384,13 @@
         <v>2040</v>
       </c>
       <c r="B83" s="12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C83" s="12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D83" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E83">
         <v>12.393484781787009</v>
@@ -7286,13 +7401,13 @@
         <v>2040</v>
       </c>
       <c r="B84" s="12" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C84" s="12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D84" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E84">
         <v>0</v>
@@ -7303,13 +7418,13 @@
         <v>2040</v>
       </c>
       <c r="B85" s="12" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C85" s="12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D85" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E85">
         <v>0</v>
@@ -7320,13 +7435,13 @@
         <v>2040</v>
       </c>
       <c r="B86" s="12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C86" s="12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D86" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E86">
         <v>0</v>
@@ -7337,13 +7452,13 @@
         <v>2040</v>
       </c>
       <c r="B87" s="12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C87" s="12" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D87" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E87">
         <v>7.5610706908851792</v>
@@ -7354,13 +7469,13 @@
         <v>2040</v>
       </c>
       <c r="B88" s="12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C88" s="12" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D88" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E88">
         <v>90.526572412455437</v>
@@ -7371,13 +7486,13 @@
         <v>2040</v>
       </c>
       <c r="B89" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C89" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D89" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E89">
         <v>4.166666666666667</v>
@@ -7388,13 +7503,13 @@
         <v>2040</v>
       </c>
       <c r="B90" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C90" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D90" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E90">
         <v>259.10866468661311</v>
@@ -7405,13 +7520,13 @@
         <v>2040</v>
       </c>
       <c r="B91" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C91" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D91" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E91">
         <v>13.682885658212991</v>
@@ -7422,13 +7537,13 @@
         <v>2045</v>
       </c>
       <c r="B92" s="12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C92" s="12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D92" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E92">
         <v>8.5006597557527961</v>
@@ -7439,13 +7554,13 @@
         <v>2045</v>
       </c>
       <c r="B93" s="12" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C93" s="12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D93" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E93">
         <v>0</v>
@@ -7456,13 +7571,13 @@
         <v>2045</v>
       </c>
       <c r="B94" s="12" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C94" s="12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D94" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E94">
         <v>0</v>
@@ -7473,13 +7588,13 @@
         <v>2045</v>
       </c>
       <c r="B95" s="12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C95" s="12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D95" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E95">
         <v>0</v>
@@ -7490,13 +7605,13 @@
         <v>2045</v>
       </c>
       <c r="B96" s="12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C96" s="12" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D96" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E96">
         <v>5.6319616755606097</v>
@@ -7507,13 +7622,13 @@
         <v>2045</v>
       </c>
       <c r="B97" s="12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C97" s="12" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D97" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E97">
         <v>67.429892840629407</v>
@@ -7524,13 +7639,13 @@
         <v>2045</v>
       </c>
       <c r="B98" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C98" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D98" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E98">
         <v>4.166666666666667</v>
@@ -7541,13 +7656,13 @@
         <v>2045</v>
       </c>
       <c r="B99" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C99" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D99" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E99">
         <v>193.00045310776611</v>
@@ -7558,13 +7673,13 @@
         <v>2045</v>
       </c>
       <c r="B100" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C100" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D100" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E100">
         <v>9.3850565442472025</v>
@@ -7575,13 +7690,13 @@
         <v>2050</v>
       </c>
       <c r="B101" s="12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C101" s="12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D101" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E101">
         <v>5.2945372674418714</v>
@@ -7592,13 +7707,13 @@
         <v>2050</v>
       </c>
       <c r="B102" s="12" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C102" s="12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D102" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E102">
         <v>0</v>
@@ -7609,13 +7724,13 @@
         <v>2050</v>
       </c>
       <c r="B103" s="12" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C103" s="12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D103" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E103">
         <v>0</v>
@@ -7626,13 +7741,13 @@
         <v>2050</v>
       </c>
       <c r="B104" s="12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C104" s="12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D104" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E104">
         <v>0</v>
@@ -7643,13 +7758,13 @@
         <v>2050</v>
       </c>
       <c r="B105" s="12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C105" s="12" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D105" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E105">
         <v>5.4810375941911236</v>
@@ -7660,13 +7775,13 @@
         <v>2050</v>
       </c>
       <c r="B106" s="12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C106" s="12" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D106" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E106">
         <v>65.622921270141603</v>
@@ -7677,13 +7792,13 @@
         <v>2050</v>
       </c>
       <c r="B107" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C107" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D107" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E107">
         <v>4.166666666666667</v>
@@ -7694,13 +7809,13 @@
         <v>2050</v>
       </c>
       <c r="B108" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C108" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D108" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E108">
         <v>187.8284690341556</v>
@@ -7711,1856 +7826,1862 @@
         <v>2050</v>
       </c>
       <c r="B109" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C109" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D109" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E109">
         <v>5.8453735425581277</v>
       </c>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>2026</v>
       </c>
       <c r="B110" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C110" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D110" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E110">
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>2026</v>
       </c>
       <c r="B111" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C111" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D111" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E111">
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112">
         <v>2026</v>
       </c>
       <c r="B112" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C112" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D112" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E112">
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113">
         <v>2026</v>
       </c>
       <c r="B113" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C113" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D113" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E113">
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114">
         <v>2026</v>
       </c>
       <c r="B114" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C114" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D114" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E114">
         <v>0.78632377625652949</v>
       </c>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115">
         <v>2026</v>
       </c>
       <c r="B115" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C115" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D115" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E115">
         <v>9.4144333760472563</v>
       </c>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116">
         <v>2026</v>
       </c>
       <c r="B116" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C116" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D116" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E116">
         <v>1.1111111111111109</v>
       </c>
     </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117">
         <v>2026</v>
       </c>
       <c r="B117" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C117" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D117" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E117">
         <v>26.946356145403541</v>
       </c>
     </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118">
         <v>2026</v>
       </c>
       <c r="B118" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C118" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D118" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E118">
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119">
         <v>2030</v>
       </c>
       <c r="B119" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C119" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D119" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E119">
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120">
         <v>2030</v>
       </c>
       <c r="B120" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C120" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D120" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E120">
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121">
         <v>2030</v>
       </c>
       <c r="B121" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C121" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D121" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E121">
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122">
         <v>2030</v>
       </c>
       <c r="B122" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C122" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D122" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E122">
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123">
         <v>2030</v>
       </c>
       <c r="B123" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C123" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D123" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E123">
         <v>1.4844705073478279</v>
       </c>
     </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124">
         <v>2030</v>
       </c>
       <c r="B124" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C124" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D124" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E124">
         <v>17.773147795004309</v>
       </c>
     </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125">
         <v>2030</v>
       </c>
       <c r="B125" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C125" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D125" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E125">
         <v>2.2222222222222219</v>
       </c>
     </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126">
         <v>2030</v>
       </c>
       <c r="B126" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C126" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D126" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E126">
         <v>50.870992568451292</v>
       </c>
     </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127">
         <v>2030</v>
       </c>
       <c r="B127" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C127" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D127" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E127">
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A128">
         <v>2035</v>
       </c>
       <c r="B128" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C128" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D128" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E128">
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129">
         <v>2035</v>
       </c>
       <c r="B129" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C129" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D129" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E129">
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A130">
         <v>2035</v>
       </c>
       <c r="B130" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C130" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D130" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E130">
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131">
         <v>2035</v>
       </c>
       <c r="B131" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C131" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D131" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E131">
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A132">
         <v>2035</v>
       </c>
       <c r="B132" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C132" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D132" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E132">
         <v>1.470180788882288</v>
       </c>
     </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A133">
         <v>2035</v>
       </c>
       <c r="B133" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C133" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D133" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E133">
         <v>17.602061015590419</v>
       </c>
     </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134">
         <v>2035</v>
       </c>
       <c r="B134" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C134" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D134" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E134">
         <v>3.333333333333333</v>
       </c>
     </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A135">
         <v>2035</v>
       </c>
       <c r="B135" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C135" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D135" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E135">
         <v>50.381301356488777</v>
       </c>
     </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136">
         <v>2035</v>
       </c>
       <c r="B136" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C136" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D136" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E136">
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137" s="12">
         <v>2040</v>
       </c>
       <c r="B137" s="12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C137" s="12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D137" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E137">
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A138" s="12">
         <v>2040</v>
       </c>
       <c r="B138" s="12" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C138" s="12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D138" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E138">
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A139" s="12">
         <v>2040</v>
       </c>
       <c r="B139" s="12" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C139" s="12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D139" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E139">
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A140" s="12">
         <v>2040</v>
       </c>
       <c r="B140" s="12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C140" s="12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D140" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E140">
         <v>0</v>
       </c>
     </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141" s="12">
         <v>2040</v>
       </c>
       <c r="B141" s="12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C141" s="12" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D141" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E141">
         <v>0.89285945878639206</v>
       </c>
     </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A142" s="12">
         <v>2040</v>
       </c>
       <c r="B142" s="12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C142" s="12" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D142" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E142">
         <v>10.68995513392159</v>
       </c>
     </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A143" s="12">
         <v>2040</v>
       </c>
       <c r="B143" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C143" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D143" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E143">
         <v>3.8888888888888888</v>
       </c>
     </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A144" s="12">
         <v>2040</v>
       </c>
       <c r="B144" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C144" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D144" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E144">
         <v>30.597203964491701</v>
       </c>
     </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A145" s="12">
         <v>2040</v>
       </c>
       <c r="B145" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C145" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D145" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E145">
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A146" s="12">
         <v>2045</v>
       </c>
       <c r="B146" s="12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C146" s="12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D146" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E146">
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A147" s="12">
         <v>2045</v>
       </c>
       <c r="B147" s="12" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C147" s="12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D147" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E147">
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A148" s="12">
         <v>2045</v>
       </c>
       <c r="B148" s="12" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C148" s="12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D148" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E148">
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A149" s="12">
         <v>2045</v>
       </c>
       <c r="B149" s="12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C149" s="12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D149" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E149">
         <v>0</v>
       </c>
     </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A150" s="12">
         <v>2045</v>
       </c>
       <c r="B150" s="12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C150" s="12" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D150" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E150">
         <v>0.43653689984869187</v>
       </c>
     </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A151" s="12">
         <v>2045</v>
       </c>
       <c r="B151" s="12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C151" s="12" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D151" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E151">
         <v>5.2265335017301622</v>
       </c>
     </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A152" s="12">
         <v>2045</v>
       </c>
       <c r="B152" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C152" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D152" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E152">
         <v>3.6111111111111112</v>
       </c>
     </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A153" s="12">
         <v>2045</v>
       </c>
       <c r="B153" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C153" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D153" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E153">
         <v>14.95958678743504</v>
       </c>
     </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A154" s="12">
         <v>2045</v>
       </c>
       <c r="B154" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C154" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D154" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E154">
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A155" s="12">
         <v>2050</v>
       </c>
       <c r="B155" s="12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C155" s="12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D155" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E155">
         <v>0</v>
       </c>
     </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A156" s="12">
         <v>2050</v>
       </c>
       <c r="B156" s="12" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C156" s="12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D156" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E156">
         <v>0</v>
       </c>
     </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A157" s="12">
         <v>2050</v>
       </c>
       <c r="B157" s="12" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C157" s="12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D157" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E157">
         <v>0</v>
       </c>
     </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A158" s="12">
         <v>2050</v>
       </c>
       <c r="B158" s="12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C158" s="12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D158" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E158">
         <v>0</v>
       </c>
     </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A159" s="12">
         <v>2050</v>
       </c>
       <c r="B159" s="12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C159" s="12" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D159" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E159">
         <v>0.26866807811826832</v>
       </c>
     </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A160" s="12">
         <v>2050</v>
       </c>
       <c r="B160" s="12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C160" s="12" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D160" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E160">
         <v>3.2166873215466931</v>
       </c>
     </row>
-    <row r="161" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A161" s="12">
         <v>2050</v>
       </c>
       <c r="B161" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C161" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D161" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E161">
         <v>3.333333333333333</v>
       </c>
     </row>
-    <row r="162" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A162" s="12">
         <v>2050</v>
       </c>
       <c r="B162" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C162" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D162" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E162">
         <v>9.2069271418216783</v>
       </c>
     </row>
-    <row r="163" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A163" s="12">
         <v>2050</v>
       </c>
       <c r="B163" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C163" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D163" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E163">
         <v>0</v>
       </c>
     </row>
-    <row r="164" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A164">
         <v>2026</v>
       </c>
       <c r="B164" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C164" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D164" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E164">
         <v>164.75172986911201</v>
       </c>
     </row>
-    <row r="165" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A165">
         <v>2026</v>
       </c>
       <c r="B165" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C165" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D165" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E165">
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A166">
         <v>2026</v>
       </c>
       <c r="B166" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C166" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D166" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E166">
         <v>0</v>
       </c>
     </row>
-    <row r="167" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A167">
         <v>2026</v>
       </c>
       <c r="B167" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C167" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D167" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E167">
         <v>0</v>
       </c>
     </row>
-    <row r="168" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A168">
         <v>2026</v>
       </c>
       <c r="B168" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C168" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D168" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E168">
         <v>24.141085746979751</v>
       </c>
     </row>
-    <row r="169" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A169">
         <v>2026</v>
       </c>
       <c r="B169" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C169" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D169" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E169">
         <v>289.03442863240991</v>
       </c>
     </row>
-    <row r="170" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A170">
         <v>2026</v>
       </c>
       <c r="B170" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C170" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D170" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E170">
         <v>3.6999999999999998E-2</v>
       </c>
     </row>
-    <row r="171" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A171">
         <v>2026</v>
       </c>
       <c r="B171" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C171" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D171" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E171">
         <v>827.28554562061026</v>
       </c>
     </row>
-    <row r="172" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A172">
         <v>2026</v>
       </c>
       <c r="B172" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C172" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D172" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E172">
         <v>181.89227013088811</v>
       </c>
     </row>
-    <row r="173" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A173">
         <v>2030</v>
       </c>
       <c r="B173" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C173" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D173" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E173">
         <v>180.38285541545281</v>
       </c>
     </row>
-    <row r="174" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A174">
         <v>2030</v>
       </c>
       <c r="B174" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C174" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D174" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E174">
         <v>0</v>
       </c>
     </row>
-    <row r="175" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A175">
         <v>2030</v>
       </c>
       <c r="B175" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C175" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D175" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E175">
         <v>0</v>
       </c>
     </row>
-    <row r="176" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A176">
         <v>2030</v>
       </c>
       <c r="B176" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C176" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D176" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E176">
         <v>0</v>
       </c>
     </row>
-    <row r="177" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A177">
         <v>2030</v>
       </c>
       <c r="B177" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C177" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D177" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E177">
         <v>13.82385009432965</v>
       </c>
     </row>
-    <row r="178" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A178">
         <v>2030</v>
       </c>
       <c r="B178" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C178" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D178" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E178">
         <v>165.5090684566469</v>
       </c>
     </row>
-    <row r="179" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A179">
         <v>2030</v>
       </c>
       <c r="B179" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C179" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D179" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E179">
         <v>0</v>
       </c>
     </row>
-    <row r="180" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A180">
         <v>2030</v>
       </c>
       <c r="B180" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C180" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D180" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E180">
         <v>473.72647144902339</v>
       </c>
     </row>
-    <row r="181" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A181">
         <v>2030</v>
       </c>
       <c r="B181" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C181" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D181" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E181">
         <v>199.14963618454729</v>
       </c>
     </row>
-    <row r="182" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A182">
         <v>2035</v>
       </c>
       <c r="B182" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C182" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D182" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E182">
         <v>140.6104754109173</v>
       </c>
     </row>
-    <row r="183" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A183">
         <v>2035</v>
       </c>
       <c r="B183" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C183" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D183" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E183">
         <v>0</v>
       </c>
     </row>
-    <row r="184" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A184">
         <v>2035</v>
       </c>
       <c r="B184" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C184" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D184" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E184">
         <v>0</v>
       </c>
     </row>
-    <row r="185" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A185">
         <v>2035</v>
       </c>
       <c r="B185" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C185" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D185" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E185">
         <v>0</v>
       </c>
     </row>
-    <row r="186" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A186">
         <v>2035</v>
       </c>
       <c r="B186" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C186" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D186" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E186">
         <v>5.6688297352257022</v>
       </c>
     </row>
-    <row r="187" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A187">
         <v>2035</v>
       </c>
       <c r="B187" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C187" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D187" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E187">
         <v>67.871303747817734</v>
       </c>
     </row>
-    <row r="188" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A188">
         <v>2035</v>
       </c>
       <c r="B188" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C188" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D188" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E188">
         <v>0</v>
       </c>
     </row>
-    <row r="189" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A189">
         <v>2035</v>
       </c>
       <c r="B189" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C189" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D189" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E189">
         <v>194.2638765169566</v>
       </c>
     </row>
-    <row r="190" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A190">
         <v>2035</v>
       </c>
       <c r="B190" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C190" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D190" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E190">
         <v>155.2393932190827</v>
       </c>
     </row>
-    <row r="191" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A191" s="12">
         <v>2040</v>
       </c>
       <c r="B191" s="12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C191" s="12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D191" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E191">
         <v>77.982331301204681</v>
       </c>
     </row>
-    <row r="192" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A192" s="12">
         <v>2040</v>
       </c>
       <c r="B192" s="12" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C192" s="12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D192" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E192">
         <v>0</v>
       </c>
     </row>
-    <row r="193" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A193" s="12">
         <v>2040</v>
       </c>
       <c r="B193" s="12" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C193" s="12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D193" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E193">
         <v>0</v>
       </c>
     </row>
-    <row r="194" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A194" s="12">
         <v>2040</v>
       </c>
       <c r="B194" s="12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C194" s="12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D194" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E194">
         <v>0</v>
       </c>
     </row>
-    <row r="195" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A195" s="12">
         <v>2040</v>
       </c>
       <c r="B195" s="12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C195" s="12" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D195" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E195">
         <v>1.6380941094450781</v>
       </c>
     </row>
-    <row r="196" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A196" s="12">
         <v>2040</v>
       </c>
       <c r="B196" s="12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C196" s="12" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D196" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E196">
         <v>19.612439967776059</v>
       </c>
     </row>
-    <row r="197" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A197" s="12">
         <v>2040</v>
       </c>
       <c r="B197" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C197" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D197" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E197">
         <v>0</v>
       </c>
     </row>
-    <row r="198" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A198" s="12">
         <v>2040</v>
       </c>
       <c r="B198" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C198" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D198" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E198">
         <v>56.135485922778869</v>
       </c>
     </row>
-    <row r="199" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A199" s="12">
         <v>2040</v>
       </c>
       <c r="B199" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C199" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D199" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E199">
         <v>86.095504318795321</v>
       </c>
     </row>
-    <row r="200" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A200" s="12">
         <v>2045</v>
       </c>
       <c r="B200" s="12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C200" s="12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D200" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E200">
         <v>29.42410936394722</v>
       </c>
     </row>
-    <row r="201" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A201" s="12">
         <v>2045</v>
       </c>
       <c r="B201" s="12" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C201" s="12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D201" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E201">
         <v>0</v>
       </c>
     </row>
-    <row r="202" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A202" s="12">
         <v>2045</v>
       </c>
       <c r="B202" s="12" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C202" s="12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D202" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E202">
         <v>0</v>
       </c>
     </row>
-    <row r="203" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A203" s="12">
         <v>2045</v>
       </c>
       <c r="B203" s="12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C203" s="12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D203" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E203">
         <v>0</v>
       </c>
     </row>
-    <row r="204" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A204" s="12">
         <v>2045</v>
       </c>
       <c r="B204" s="12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C204" s="12" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D204" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E204">
         <v>1.9202185232449069</v>
       </c>
     </row>
-    <row r="205" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A205" s="12">
         <v>2045</v>
       </c>
       <c r="B205" s="12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C205" s="12" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D205" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E205">
         <v>22.99023621109907</v>
       </c>
     </row>
-    <row r="206" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A206" s="12">
         <v>2045</v>
       </c>
       <c r="B206" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C206" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D206" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E206">
         <v>0</v>
       </c>
     </row>
-    <row r="207" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A207" s="12">
         <v>2045</v>
       </c>
       <c r="B207" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C207" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D207" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E207">
         <v>65.803545265656012</v>
       </c>
     </row>
-    <row r="208" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A208" s="12">
         <v>2045</v>
       </c>
       <c r="B208" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C208" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D208" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E208">
         <v>32.485352676052777</v>
       </c>
     </row>
-    <row r="209" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A209" s="12">
         <v>2050</v>
       </c>
       <c r="B209" s="12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C209" s="12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D209" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E209">
         <v>1.328835503507124</v>
       </c>
     </row>
-    <row r="210" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A210" s="12">
         <v>2050</v>
       </c>
       <c r="B210" s="12" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C210" s="12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D210" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E210">
         <v>0</v>
       </c>
     </row>
-    <row r="211" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A211" s="12">
         <v>2050</v>
       </c>
       <c r="B211" s="12" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C211" s="12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D211" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E211">
         <v>0</v>
       </c>
     </row>
-    <row r="212" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A212" s="12">
         <v>2050</v>
       </c>
       <c r="B212" s="12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C212" s="12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D212" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E212">
         <v>0</v>
       </c>
     </row>
-    <row r="213" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A213" s="12">
         <v>2050</v>
       </c>
       <c r="B213" s="12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C213" s="12" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D213" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E213">
         <v>1.945821436888173</v>
       </c>
     </row>
-    <row r="214" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A214" s="12">
         <v>2050</v>
       </c>
       <c r="B214" s="12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C214" s="12" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D214" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E214">
         <v>23.29677269391372</v>
       </c>
     </row>
-    <row r="215" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A215" s="12">
         <v>2050</v>
       </c>
       <c r="B215" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C215" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D215" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E215">
         <v>0</v>
       </c>
     </row>
-    <row r="216" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A216" s="12">
         <v>2050</v>
       </c>
       <c r="B216" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C216" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D216" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E216">
         <v>66.680925869198092</v>
       </c>
     </row>
-    <row r="217" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A217" s="12">
         <v>2050</v>
       </c>
       <c r="B217" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C217" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D217" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E217">
         <v>1.4670856964928769</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B1:B217" xr:uid="{1F3C079C-E0FE-4643-9E48-5AE3F12A3520}"/>
+  <autoFilter ref="D1:D217" xr:uid="{1F3C079C-E0FE-4643-9E48-5AE3F12A3520}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="Industry"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
@@ -9573,21 +9694,21 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C2">
         <v>968</v>
@@ -9595,10 +9716,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C3">
         <v>1579</v>
@@ -9606,10 +9727,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C4">
         <v>1389</v>
@@ -9617,10 +9738,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C5">
         <v>1579</v>
@@ -9628,10 +9749,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C6">
         <v>1389</v>
@@ -9639,10 +9760,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C7">
         <v>968</v>
@@ -9650,10 +9771,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C8">
         <v>818</v>
@@ -9661,10 +9782,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C9">
         <v>781</v>
@@ -9672,10 +9793,10 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C10">
         <v>297</v>
@@ -9686,7 +9807,7 @@
         <v>2</v>
       </c>
       <c r="B12" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
   </sheetData>
@@ -9704,24 +9825,24 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>126</v>
-      </c>
       <c r="E1" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B2">
         <v>31</v>
@@ -9738,7 +9859,7 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B3">
         <v>31</v>

--- a/scm_input_cleaned.xlsx
+++ b/scm_input_cleaned.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5611d695511771a1/Desktop/Repositories/scm_model/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="514" documentId="8_{69118542-9163-4E18-BF71-86AAA6BFC266}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E97B9C10-CE61-45B9-A45C-8F7B09F94EC0}"/>
+  <xr:revisionPtr revIDLastSave="525" documentId="8_{69118542-9163-4E18-BF71-86AAA6BFC266}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7A2DBF90-A9BA-4883-A216-4AFD2263B6C8}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="6825" windowWidth="29040" windowHeight="17520" xr2:uid="{D3628906-A666-41FC-B4DD-112A108B04C0}"/>
   </bookViews>
@@ -250,7 +250,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1022" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1022" uniqueCount="151">
   <si>
     <t>year</t>
   </si>
@@ -288,9 +288,6 @@
     <t>ETS low</t>
   </si>
   <si>
-    <t xml:space="preserve">ETS mid </t>
-  </si>
-  <si>
     <t>ETS high</t>
   </si>
   <si>
@@ -700,6 +697,12 @@
   </si>
   <si>
     <t>opex_var_2050</t>
+  </si>
+  <si>
+    <t>Download | ENTSOs TYNDP Scenarios 2026</t>
+  </si>
+  <si>
+    <t>ENTSOE CO2 Price Trajectory</t>
   </si>
 </sst>
 </file>
@@ -711,7 +714,7 @@
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -762,12 +765,6 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Segoe UI"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -1257,37 +1254,37 @@
         <v>7</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="I1" s="1" t="s">
-        <v>22</v>
-      </c>
       <c r="J1" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>54</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
@@ -1303,7 +1300,7 @@
       <c r="D2" s="5">
         <v>80</v>
       </c>
-      <c r="E2" s="5">
+      <c r="E2">
         <v>80</v>
       </c>
       <c r="F2" s="5">
@@ -1349,8 +1346,8 @@
       <c r="D3" s="5">
         <v>88</v>
       </c>
-      <c r="E3" s="5">
-        <v>82.786665885632303</v>
+      <c r="E3">
+        <v>84.37</v>
       </c>
       <c r="F3" s="5">
         <v>130</v>
@@ -1395,8 +1392,8 @@
       <c r="D4" s="5">
         <v>97</v>
       </c>
-      <c r="E4" s="5">
-        <v>89.708296579282504</v>
+      <c r="E4">
+        <v>88.74</v>
       </c>
       <c r="F4" s="5">
         <v>185</v>
@@ -1441,8 +1438,8 @@
       <c r="D5" s="5">
         <v>108</v>
       </c>
-      <c r="E5" s="5">
-        <v>94.199581355889293</v>
+      <c r="E5">
+        <v>93.1</v>
       </c>
       <c r="F5" s="5">
         <v>220</v>
@@ -1487,8 +1484,8 @@
       <c r="D6" s="5">
         <v>120</v>
       </c>
-      <c r="E6" s="5">
-        <v>97.999586047999998</v>
+      <c r="E6">
+        <v>97.47</v>
       </c>
       <c r="F6" s="5">
         <v>261</v>
@@ -1533,8 +1530,8 @@
       <c r="D7" s="5">
         <v>126</v>
       </c>
-      <c r="E7" s="5">
-        <v>111.224283671058</v>
+      <c r="E7">
+        <v>117.48</v>
       </c>
       <c r="F7" s="5">
         <v>280</v>
@@ -1579,8 +1576,8 @@
       <c r="D8" s="5">
         <v>133</v>
       </c>
-      <c r="E8" s="5">
-        <v>131.181845885538</v>
+      <c r="E8">
+        <v>137.49</v>
       </c>
       <c r="F8" s="5">
         <v>300</v>
@@ -1625,8 +1622,8 @@
       <c r="D9" s="5">
         <v>141</v>
       </c>
-      <c r="E9" s="5">
-        <v>156.78809085472099</v>
+      <c r="E9">
+        <v>157.49</v>
       </c>
       <c r="F9" s="5">
         <v>330</v>
@@ -1671,8 +1668,8 @@
       <c r="D10" s="5">
         <v>150</v>
       </c>
-      <c r="E10" s="5">
-        <v>183.77078989175399</v>
+      <c r="E10">
+        <v>177.5</v>
       </c>
       <c r="F10" s="5">
         <v>380</v>
@@ -1717,8 +1714,8 @@
       <c r="D11" s="5">
         <v>159</v>
       </c>
-      <c r="E11" s="5">
-        <v>211.02665861961299</v>
+      <c r="E11">
+        <v>197.51</v>
       </c>
       <c r="F11" s="5">
         <v>400</v>
@@ -1763,8 +1760,8 @@
       <c r="D12" s="5">
         <v>169</v>
       </c>
-      <c r="E12" s="5">
-        <v>238.08698903057294</v>
+      <c r="E12">
+        <v>217.52</v>
       </c>
       <c r="F12" s="5">
         <v>410</v>
@@ -1809,8 +1806,8 @@
       <c r="D13" s="5">
         <v>181</v>
       </c>
-      <c r="E13" s="5">
-        <v>264.51020974760536</v>
+      <c r="E13">
+        <v>237.52</v>
       </c>
       <c r="F13" s="5">
         <v>420</v>
@@ -1855,8 +1852,8 @@
       <c r="D14">
         <v>195</v>
       </c>
-      <c r="E14" s="5">
-        <v>288.79758011384274</v>
+      <c r="E14">
+        <v>257.52999999999997</v>
       </c>
       <c r="F14" s="5">
         <v>425</v>
@@ -1901,8 +1898,8 @@
       <c r="D15" s="5">
         <v>211</v>
       </c>
-      <c r="E15" s="5">
-        <v>300.99957621804123</v>
+      <c r="E15">
+        <v>277.52999999999997</v>
       </c>
       <c r="F15" s="5">
         <v>430</v>
@@ -1947,8 +1944,8 @@
       <c r="D16" s="5">
         <v>227</v>
       </c>
-      <c r="E16" s="5">
-        <v>305.38871003261175</v>
+      <c r="E16">
+        <v>297.54000000000002</v>
       </c>
       <c r="F16">
         <v>435</v>
@@ -1993,8 +1990,8 @@
       <c r="D17" s="5">
         <v>245</v>
       </c>
-      <c r="E17" s="5">
-        <v>311.19461215067878</v>
+      <c r="E17">
+        <v>318.06</v>
       </c>
       <c r="F17" s="5">
         <v>440</v>
@@ -2039,8 +2036,8 @@
       <c r="D18" s="5">
         <v>262</v>
       </c>
-      <c r="E18" s="5">
-        <v>319.89624213683373</v>
+      <c r="E18">
+        <v>338.58</v>
       </c>
       <c r="F18" s="5">
         <v>445</v>
@@ -2085,8 +2082,8 @@
       <c r="D19" s="5">
         <v>279</v>
       </c>
-      <c r="E19" s="5">
-        <v>329.95643893995231</v>
+      <c r="E19">
+        <v>359.1</v>
       </c>
       <c r="F19" s="5">
         <v>450</v>
@@ -2131,8 +2128,8 @@
       <c r="D20" s="5">
         <v>295</v>
       </c>
-      <c r="E20" s="5">
-        <v>340.28677129307425</v>
+      <c r="E20">
+        <v>379.62</v>
       </c>
       <c r="F20" s="5">
         <v>455</v>
@@ -2177,8 +2174,8 @@
       <c r="D21" s="5">
         <v>312</v>
       </c>
-      <c r="E21" s="5">
-        <v>350.32853261653543</v>
+      <c r="E21">
+        <v>400.14</v>
       </c>
       <c r="F21" s="5">
         <v>460</v>
@@ -2223,8 +2220,8 @@
       <c r="D22" s="5">
         <v>327</v>
       </c>
-      <c r="E22" s="5">
-        <v>359.81403573037062</v>
+      <c r="E22">
+        <v>420.66</v>
       </c>
       <c r="F22" s="5">
         <v>464</v>
@@ -2269,8 +2266,8 @@
       <c r="D23" s="5">
         <v>342</v>
       </c>
-      <c r="E23" s="5">
-        <v>368.42082962055105</v>
+      <c r="E23">
+        <v>441.18</v>
       </c>
       <c r="F23" s="5">
         <v>467</v>
@@ -2315,8 +2312,8 @@
       <c r="D24" s="5">
         <v>356</v>
       </c>
-      <c r="E24" s="5">
-        <v>376.18236299340958</v>
+      <c r="E24">
+        <v>461.7</v>
       </c>
       <c r="F24" s="5">
         <v>470</v>
@@ -2361,8 +2358,8 @@
       <c r="D25" s="5">
         <v>368</v>
       </c>
-      <c r="E25" s="5">
-        <v>383.15257074956276</v>
+      <c r="E25">
+        <v>482.22</v>
       </c>
       <c r="F25" s="5">
         <v>473</v>
@@ -2406,8 +2403,8 @@
       <c r="D26">
         <v>379</v>
       </c>
-      <c r="E26" s="5">
-        <v>389.43894440381348</v>
+      <c r="E26">
+        <v>502.74</v>
       </c>
       <c r="F26">
         <v>475</v>
@@ -2450,16 +2447,16 @@
         <v>8</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>9</v>
+        <v>149</v>
       </c>
       <c r="F27" s="4" t="s">
         <v>10</v>
       </c>
       <c r="G27" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H27" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I27" s="4" t="s">
         <v>9</v>
@@ -2479,36 +2476,36 @@
         <v>11</v>
       </c>
       <c r="E28" t="s">
+        <v>150</v>
+      </c>
+      <c r="F28" t="s">
         <v>12</v>
       </c>
-      <c r="F28" t="s">
-        <v>13</v>
-      </c>
       <c r="G28" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J28" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="G29" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H29" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I29" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="C27" r:id="rId1" location="sources-and-processing" xr:uid="{2A69B3B0-17E4-4DF3-9900-1F80A399FA35}"/>
-    <hyperlink ref="E27" r:id="rId2" xr:uid="{0B6D8AE3-55AE-41A3-AD66-8CD368DD2907}"/>
-    <hyperlink ref="F27" r:id="rId3" xr:uid="{452EDB1E-1B56-4646-86B8-4BACAF7A6854}"/>
-    <hyperlink ref="D27" r:id="rId4" xr:uid="{140E2839-83FE-46C3-B4D0-2969D425F9A8}"/>
-    <hyperlink ref="I27" r:id="rId5" xr:uid="{EE46F9E4-2010-4731-91A1-D20CAA7A143D}"/>
+    <hyperlink ref="F27" r:id="rId2" xr:uid="{452EDB1E-1B56-4646-86B8-4BACAF7A6854}"/>
+    <hyperlink ref="D27" r:id="rId3" xr:uid="{140E2839-83FE-46C3-B4D0-2969D425F9A8}"/>
+    <hyperlink ref="I27" r:id="rId4" xr:uid="{EE46F9E4-2010-4731-91A1-D20CAA7A143D}"/>
+    <hyperlink ref="E27" r:id="rId5" display="https://2026.entsos-tyndp-scenarios.eu/download/" xr:uid="{FC204606-9E86-4230-A5A2-1AF5BC272C10}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId6"/>
@@ -2528,63 +2525,63 @@
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="H1" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="I1" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>83</v>
-      </c>
       <c r="M1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="N1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>47</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C2">
         <v>2</v>
       </c>
       <c r="D2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E2" s="9">
         <f>2034-2026</f>
@@ -2623,16 +2620,16 @@
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
       <c r="D3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E3" s="9">
         <v>-1</v>
@@ -2670,16 +2667,16 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C4">
         <v>2</v>
       </c>
       <c r="D4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E4" s="9">
         <f>2030-2026</f>
@@ -2718,16 +2715,16 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C5">
         <v>1</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E5" s="9">
         <f>2030-2026</f>
@@ -2766,16 +2763,16 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C6">
         <v>1</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E6" s="9">
         <f>2033-2026</f>
@@ -2814,16 +2811,16 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C7">
         <v>1</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E7" s="9">
         <f>2028-2026</f>
@@ -2862,16 +2859,16 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C8">
         <v>1</v>
       </c>
       <c r="D8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E8" s="9">
         <f>2030-2026</f>
@@ -2910,16 +2907,16 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C9">
         <v>1</v>
       </c>
       <c r="D9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E9" s="9">
         <v>-1</v>
@@ -2957,16 +2954,16 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C10">
         <v>1</v>
       </c>
       <c r="D10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E10" s="9">
         <f>2030-2026</f>
@@ -3005,16 +3002,16 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C11">
         <v>1</v>
       </c>
       <c r="D11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E11" s="9">
         <f>2030-2026</f>
@@ -3053,16 +3050,16 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C12">
         <v>1</v>
       </c>
       <c r="D12" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E12" s="9">
         <f>2030-2026</f>
@@ -3101,16 +3098,16 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C13">
         <v>1</v>
       </c>
       <c r="D13" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E13" s="9">
         <v>-1</v>
@@ -3148,16 +3145,16 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C14">
         <v>2</v>
       </c>
       <c r="D14" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E14" s="9">
         <f>2030-2026</f>
@@ -3196,16 +3193,16 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C15">
         <v>1</v>
       </c>
       <c r="D15" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E15" s="9">
         <f>2028-2026</f>
@@ -3244,16 +3241,16 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C16">
         <v>2</v>
       </c>
       <c r="D16" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E16" s="9">
         <f>2030-2026</f>
@@ -3292,16 +3289,16 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C17">
         <v>1</v>
       </c>
       <c r="D17" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E17" s="9">
         <f>2030-2026</f>
@@ -3340,16 +3337,16 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C18">
         <v>1</v>
       </c>
       <c r="D18" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E18" s="9">
         <f>2029-2026</f>
@@ -3388,16 +3385,16 @@
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C19">
         <v>1</v>
       </c>
       <c r="D19" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E19" s="9">
         <f>2031-2026</f>
@@ -3436,16 +3433,16 @@
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C20">
         <v>1</v>
       </c>
       <c r="D20" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E20" s="9">
         <f>2031-2026</f>
@@ -3484,16 +3481,16 @@
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C21">
         <v>1</v>
       </c>
       <c r="D21" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E21">
         <f>2032-2026</f>
@@ -3532,16 +3529,16 @@
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C22">
         <v>1</v>
       </c>
       <c r="D22" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E22" s="9">
         <f>2029-2026</f>
@@ -3580,16 +3577,16 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C23">
         <v>1</v>
       </c>
       <c r="D23" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E23" s="9">
         <f>2029-2026</f>
@@ -3628,16 +3625,16 @@
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C24">
         <v>1</v>
       </c>
       <c r="D24" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E24">
         <f>2034-2026</f>
@@ -3676,16 +3673,16 @@
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C25">
         <v>1</v>
       </c>
       <c r="D25" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E25" s="9">
         <f>2030-2026</f>
@@ -3724,16 +3721,16 @@
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C26">
         <v>2</v>
       </c>
       <c r="D26" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E26" s="9">
         <v>8</v>
@@ -3771,16 +3768,16 @@
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C27">
         <v>1</v>
       </c>
       <c r="D27" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E27" s="9">
         <f>2031-2026</f>
@@ -3819,16 +3816,16 @@
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C28">
         <v>1</v>
       </c>
       <c r="D28" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E28" s="9">
         <f>2029-2026</f>
@@ -3867,16 +3864,16 @@
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C29">
         <v>1</v>
       </c>
       <c r="D29" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E29">
         <f>2027-2026</f>
@@ -3915,16 +3912,16 @@
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C30">
         <v>1</v>
       </c>
       <c r="D30" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E30">
         <v>9</v>
@@ -3962,16 +3959,16 @@
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C31">
         <v>1</v>
       </c>
       <c r="D31" s="8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E31" s="9">
         <f>2027-2026</f>
@@ -4010,16 +4007,16 @@
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C32">
         <v>2</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E32" s="9">
         <f>2037-2026</f>
@@ -4058,16 +4055,16 @@
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C33">
         <v>1</v>
       </c>
       <c r="D33" s="8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E33" s="9">
         <v>-1</v>
@@ -4105,16 +4102,16 @@
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C34">
         <v>2</v>
       </c>
       <c r="D34" s="8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E34" s="9">
         <f>2028-2026</f>
@@ -4153,16 +4150,16 @@
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C35">
         <v>1</v>
       </c>
       <c r="D35" s="8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E35" s="9">
         <f>2032-2026</f>
@@ -4201,16 +4198,16 @@
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C36">
         <v>1</v>
       </c>
       <c r="D36" s="8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E36" s="9">
         <f>2034-2026</f>
@@ -4249,16 +4246,16 @@
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C37">
         <v>1</v>
       </c>
       <c r="D37" s="8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E37" s="9">
         <f>2029-2026</f>
@@ -4297,16 +4294,16 @@
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C38">
         <v>1</v>
       </c>
       <c r="D38" s="8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E38" s="9">
         <v>3</v>
@@ -4344,16 +4341,16 @@
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C39">
         <v>1</v>
       </c>
       <c r="D39" s="8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E39" s="9">
         <f>2030-2026</f>
@@ -4392,16 +4389,16 @@
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C40">
         <v>1</v>
       </c>
       <c r="D40" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E40" s="9">
         <f>2027-2026</f>
@@ -4440,16 +4437,16 @@
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C41">
         <v>1</v>
       </c>
       <c r="D41" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E41" s="9">
         <f>2030-2026</f>
@@ -4488,16 +4485,16 @@
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C42">
         <v>1</v>
       </c>
       <c r="D42" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E42" s="9">
         <f>2028-2026</f>
@@ -4536,16 +4533,16 @@
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C43">
         <v>2</v>
       </c>
       <c r="D43" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E43" s="9">
         <f>2035-2026</f>
@@ -4584,16 +4581,16 @@
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C44">
         <v>1</v>
       </c>
       <c r="D44" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E44" s="9">
         <f>2027-2026</f>
@@ -4632,16 +4629,16 @@
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B45" s="8" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C45">
         <v>2</v>
       </c>
       <c r="D45" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E45" s="9">
         <f>2030-2026</f>
@@ -4680,16 +4677,16 @@
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B46" s="8" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C46">
         <v>3</v>
       </c>
       <c r="D46" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E46" s="9">
         <f>2035-2026</f>
@@ -4728,16 +4725,16 @@
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B47" s="8" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C47">
         <v>1</v>
       </c>
       <c r="D47" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E47" s="9">
         <f>2032-2026</f>
@@ -4776,16 +4773,16 @@
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B48" s="8" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C48">
         <v>1</v>
       </c>
       <c r="D48" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E48" s="9">
         <f>2030-2026</f>
@@ -4824,16 +4821,16 @@
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B49" s="8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C49">
         <v>1</v>
       </c>
       <c r="D49" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E49" s="9">
         <f>2029-2026</f>
@@ -4872,16 +4869,16 @@
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B50" s="8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C50">
         <v>2</v>
       </c>
       <c r="D50" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E50" s="9">
         <f>2034-2026</f>
@@ -4920,16 +4917,16 @@
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B51" s="8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C51">
         <v>3</v>
       </c>
       <c r="D51" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E51" s="9">
         <f>2040-2026</f>
@@ -4968,16 +4965,16 @@
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B52" s="8" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C52">
         <v>1</v>
       </c>
       <c r="D52" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E52" s="9">
         <f>2031-2026</f>
@@ -5016,16 +5013,16 @@
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B53" s="8" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C53">
         <v>2</v>
       </c>
       <c r="D53" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E53" s="9">
         <v>8</v>
@@ -5063,16 +5060,16 @@
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B54" s="8" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C54">
         <v>1</v>
       </c>
       <c r="D54" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E54" s="9">
         <f>2029-2026</f>
@@ -5111,16 +5108,16 @@
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B55" s="8" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C55">
         <v>1</v>
       </c>
       <c r="D55" s="8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E55" s="9">
         <f>2033-2026</f>
@@ -5159,16 +5156,16 @@
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B56" s="8" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C56">
         <v>1</v>
       </c>
       <c r="D56" s="8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E56" s="9">
         <f>2033-2026</f>
@@ -5207,16 +5204,16 @@
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B57" s="8" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C57">
         <v>1</v>
       </c>
       <c r="D57" s="8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E57" s="9">
         <f>2030-2026</f>
@@ -5255,16 +5252,16 @@
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B58" s="8" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C58">
         <v>2</v>
       </c>
       <c r="D58" s="8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E58" s="9">
         <v>8</v>
@@ -5302,16 +5299,16 @@
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B59" s="8" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C59">
         <v>1</v>
       </c>
       <c r="D59" s="8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E59" s="9">
         <f>2028-2026</f>
@@ -5350,16 +5347,16 @@
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B60" s="8" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C60">
         <v>2</v>
       </c>
       <c r="D60" s="8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E60" s="9">
         <f>2035-2026</f>
@@ -5413,69 +5410,69 @@
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>57</v>
-      </c>
       <c r="D1" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>51</v>
-      </c>
       <c r="H1" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="I1" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="O1" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="L1" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>148</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D2" s="6">
         <v>143</v>
@@ -5529,13 +5526,13 @@
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D3" s="6">
         <v>105</v>
@@ -5589,13 +5586,13 @@
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D4" s="6">
         <v>36</v>
@@ -5649,13 +5646,13 @@
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D5" s="6">
         <v>105</v>
@@ -5709,13 +5706,13 @@
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D6" s="6">
         <v>85</v>
@@ -5772,13 +5769,13 @@
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>103</v>
+      </c>
+      <c r="B7" t="s">
         <v>104</v>
       </c>
-      <c r="B7" t="s">
-        <v>105</v>
-      </c>
       <c r="C7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D7" s="6">
         <v>143</v>
@@ -5843,39 +5840,39 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D1" t="s">
         <v>85</v>
       </c>
-      <c r="C1" t="s">
-        <v>56</v>
-      </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>86</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>87</v>
-      </c>
-      <c r="F1" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F2">
         <v>0.8</v>
@@ -5883,19 +5880,19 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F3">
         <v>1</v>
@@ -5903,19 +5900,19 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D4">
         <v>0</v>
       </c>
       <c r="E4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F4">
         <v>0.75</v>
@@ -5923,19 +5920,19 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D5">
         <v>160000</v>
       </c>
       <c r="E5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F5">
         <v>0.5</v>
@@ -5943,19 +5940,19 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D6">
         <v>100000</v>
       </c>
       <c r="E6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F6">
         <v>1.5</v>
@@ -5963,19 +5960,19 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C7" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D7">
         <v>400000</v>
       </c>
       <c r="E7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F7">
         <v>0.4</v>
@@ -5983,19 +5980,19 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B8" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D8">
         <v>0</v>
       </c>
       <c r="E8" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F8">
         <v>0.5</v>
@@ -6003,19 +6000,19 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B9" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D9">
         <v>0</v>
       </c>
       <c r="E9" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F9">
         <v>0.5</v>
@@ -6023,19 +6020,19 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B10" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C10" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D10">
         <v>1700000</v>
       </c>
       <c r="E10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F10">
         <v>0.3</v>
@@ -6043,19 +6040,19 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B11" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C11" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D11">
         <v>0</v>
       </c>
       <c r="E11" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F11">
         <v>0.6</v>
@@ -6063,19 +6060,19 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B12" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C12" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D12">
         <v>0</v>
       </c>
       <c r="E12" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F12">
         <v>0.8</v>
@@ -6083,19 +6080,19 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B13" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C13" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D13">
         <v>0</v>
       </c>
       <c r="E13" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F13">
         <v>1</v>
@@ -6103,19 +6100,19 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B14" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C14" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D14">
         <v>0</v>
       </c>
       <c r="E14" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F14">
         <v>1</v>
@@ -6123,19 +6120,19 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B15" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C15" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D15">
         <v>0</v>
       </c>
       <c r="E15" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F15">
         <v>0.9</v>
@@ -6143,19 +6140,19 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B16" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C16" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D16">
         <v>0</v>
       </c>
       <c r="E16" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F16">
         <v>1.2</v>
@@ -6163,19 +6160,19 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B17" t="s">
+        <v>103</v>
+      </c>
+      <c r="C17" t="s">
         <v>104</v>
       </c>
-      <c r="C17" t="s">
-        <v>105</v>
-      </c>
       <c r="D17">
         <v>0</v>
       </c>
       <c r="E17" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F17">
         <v>0.5</v>
@@ -6183,19 +6180,19 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B18" t="s">
+        <v>103</v>
+      </c>
+      <c r="C18" t="s">
         <v>104</v>
       </c>
-      <c r="C18" t="s">
-        <v>105</v>
-      </c>
       <c r="D18">
         <v>0</v>
       </c>
       <c r="E18" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F18">
         <v>0.5</v>
@@ -6203,19 +6200,19 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B19" t="s">
+        <v>103</v>
+      </c>
+      <c r="C19" t="s">
         <v>104</v>
       </c>
-      <c r="C19" t="s">
-        <v>105</v>
-      </c>
       <c r="D19">
         <v>0</v>
       </c>
       <c r="E19" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F19">
         <v>0.5</v>
@@ -6238,16 +6235,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>67</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -6255,13 +6252,13 @@
         <v>2026</v>
       </c>
       <c r="B2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E2">
         <v>91.346707935673805</v>
@@ -6272,13 +6269,13 @@
         <v>2026</v>
       </c>
       <c r="B3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -6289,13 +6286,13 @@
         <v>2026</v>
       </c>
       <c r="B4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -6306,13 +6303,13 @@
         <v>2026</v>
       </c>
       <c r="B5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -6323,13 +6320,13 @@
         <v>2026</v>
       </c>
       <c r="B6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E6">
         <v>11.812967958185389</v>
@@ -6340,13 +6337,13 @@
         <v>2026</v>
       </c>
       <c r="B7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D7" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E7">
         <v>141.4333423124618</v>
@@ -6357,13 +6354,13 @@
         <v>2026</v>
       </c>
       <c r="B8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D8" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E8">
         <v>2.67</v>
@@ -6374,13 +6371,13 @@
         <v>2026</v>
       </c>
       <c r="B9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D9" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E9">
         <v>404.81599481948882</v>
@@ -6391,13 +6388,13 @@
         <v>2026</v>
       </c>
       <c r="B10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E10">
         <v>100.8502920643262</v>
@@ -6408,13 +6405,13 @@
         <v>2030</v>
       </c>
       <c r="B11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D11" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E11">
         <v>28.073099119979691</v>
@@ -6425,13 +6422,13 @@
         <v>2030</v>
       </c>
       <c r="B12" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D12" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -6442,13 +6439,13 @@
         <v>2030</v>
       </c>
       <c r="B13" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D13" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -6459,13 +6456,13 @@
         <v>2030</v>
       </c>
       <c r="B14" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C14" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D14" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -6476,13 +6473,13 @@
         <v>2030</v>
       </c>
       <c r="B15" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C15" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D15" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E15">
         <v>9.8816510339669801</v>
@@ -6493,13 +6490,13 @@
         <v>2030</v>
       </c>
       <c r="B16" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C16" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D16" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E16">
         <v>118.31022806854629</v>
@@ -6510,13 +6507,13 @@
         <v>2030</v>
       </c>
       <c r="B17" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C17" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D17" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E17">
         <v>2.14</v>
@@ -6527,13 +6524,13 @@
         <v>2030</v>
       </c>
       <c r="B18" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C18" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D18" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E18">
         <v>338.63212089748669</v>
@@ -6544,13 +6541,13 @@
         <v>2030</v>
       </c>
       <c r="B19" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C19" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D19" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E19">
         <v>30.993785210020299</v>
@@ -6561,13 +6558,13 @@
         <v>2035</v>
       </c>
       <c r="B20" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C20" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D20" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E20">
         <v>27.939162342756621</v>
@@ -6578,13 +6575,13 @@
         <v>2035</v>
       </c>
       <c r="B21" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C21" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D21" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -6595,13 +6592,13 @@
         <v>2035</v>
       </c>
       <c r="B22" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C22" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D22" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -6612,13 +6609,13 @@
         <v>2035</v>
       </c>
       <c r="B23" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C23" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D23" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -6629,13 +6626,13 @@
         <v>2035</v>
       </c>
       <c r="B24" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C24" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D24" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E24">
         <v>6.951367170491487</v>
@@ -6646,13 +6643,13 @@
         <v>2035</v>
       </c>
       <c r="B25" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C25" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D25" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E25">
         <v>83.226763675633933</v>
@@ -6663,13 +6660,13 @@
         <v>2035</v>
       </c>
       <c r="B26" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C26" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D26" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E26">
         <v>1.6</v>
@@ -6680,13 +6677,13 @@
         <v>2035</v>
       </c>
       <c r="B27" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C27" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D27" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E27">
         <v>238.2148691538745</v>
@@ -6697,13 +6694,13 @@
         <v>2035</v>
       </c>
       <c r="B28" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C28" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D28" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E28">
         <v>30.845913837243369</v>
@@ -6714,13 +6711,13 @@
         <v>2040</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D29" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E29">
         <v>47.013994948645028</v>
@@ -6731,13 +6728,13 @@
         <v>2040</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D30" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -6748,13 +6745,13 @@
         <v>2040</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D31" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -6765,13 +6762,13 @@
         <v>2040</v>
       </c>
       <c r="B32" s="11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D32" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -6782,13 +6779,13 @@
         <v>2040</v>
       </c>
       <c r="B33" s="11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D33" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E33">
         <v>5.3565405287568293</v>
@@ -6799,13 +6796,13 @@
         <v>2040</v>
       </c>
       <c r="B34" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D34" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E34">
         <v>64.132352927385313</v>
@@ -6816,13 +6813,13 @@
         <v>2040</v>
       </c>
       <c r="B35" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C35" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D35" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E35">
         <v>1.07</v>
@@ -6833,13 +6830,13 @@
         <v>2040</v>
       </c>
       <c r="B36" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C36" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D36" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E36">
         <v>183.56210654385791</v>
@@ -6850,13 +6847,13 @@
         <v>2040</v>
       </c>
       <c r="B37" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C37" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D37" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E37">
         <v>51.90526543135497</v>
@@ -6867,13 +6864,13 @@
         <v>2045</v>
       </c>
       <c r="B38" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D38" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E38">
         <v>50.179985896702192</v>
@@ -6884,13 +6881,13 @@
         <v>2045</v>
       </c>
       <c r="B39" s="11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D39" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E39">
         <v>0</v>
@@ -6901,13 +6898,13 @@
         <v>2045</v>
       </c>
       <c r="B40" s="11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D40" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E40">
         <v>0</v>
@@ -6918,13 +6915,13 @@
         <v>2045</v>
       </c>
       <c r="B41" s="11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C41" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D41" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -6935,13 +6932,13 @@
         <v>2045</v>
       </c>
       <c r="B42" s="11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D42" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E42">
         <v>4.1055641162215259</v>
@@ -6952,13 +6949,13 @@
         <v>2045</v>
       </c>
       <c r="B43" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C43" s="11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D43" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E43">
         <v>49.154764246437132</v>
@@ -6969,13 +6966,13 @@
         <v>2045</v>
       </c>
       <c r="B44" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C44" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D44" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E44">
         <v>0.53</v>
@@ -6986,13 +6983,13 @@
         <v>2045</v>
       </c>
       <c r="B45" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C45" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D45" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E45">
         <v>140.69267163734131</v>
@@ -7003,13 +7000,13 @@
         <v>2045</v>
       </c>
       <c r="B46" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C46" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D46" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E46">
         <v>55.400641663297797</v>
@@ -7020,13 +7017,13 @@
         <v>2050</v>
       </c>
       <c r="B47" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C47" s="11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D47" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E47">
         <v>47.501061705512093</v>
@@ -7037,13 +7034,13 @@
         <v>2050</v>
       </c>
       <c r="B48" s="11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C48" s="11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D48" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E48">
         <v>0</v>
@@ -7054,13 +7051,13 @@
         <v>2050</v>
       </c>
       <c r="B49" s="11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C49" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D49" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E49">
         <v>0</v>
@@ -7071,13 +7068,13 @@
         <v>2050</v>
       </c>
       <c r="B50" s="11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C50" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D50" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E50">
         <v>0</v>
@@ -7088,13 +7085,13 @@
         <v>2050</v>
       </c>
       <c r="B51" s="11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C51" s="11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D51" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E51">
         <v>3.905083599061522</v>
@@ -7105,13 +7102,13 @@
         <v>2050</v>
       </c>
       <c r="B52" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C52" s="11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D52" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E52">
         <v>46.754467410719172</v>
@@ -7122,13 +7119,13 @@
         <v>2050</v>
       </c>
       <c r="B53" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C53" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D53" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E53">
         <v>0</v>
@@ -7139,13 +7136,13 @@
         <v>2050</v>
       </c>
       <c r="B54" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C54" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D54" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E54">
         <v>133.8224489902193</v>
@@ -7156,13 +7153,13 @@
         <v>2050</v>
       </c>
       <c r="B55" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C55" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D55" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E55">
         <v>52.443005934487907</v>
@@ -7173,13 +7170,13 @@
         <v>2026</v>
       </c>
       <c r="B56" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C56" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D56" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E56">
         <v>32.492749807386559</v>
@@ -7190,13 +7187,13 @@
         <v>2026</v>
       </c>
       <c r="B57" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C57" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D57" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E57">
         <v>0</v>
@@ -7207,13 +7204,13 @@
         <v>2026</v>
       </c>
       <c r="B58" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C58" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D58" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E58">
         <v>0</v>
@@ -7224,13 +7221,13 @@
         <v>2026</v>
       </c>
       <c r="B59" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C59" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D59" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E59">
         <v>0</v>
@@ -7241,13 +7238,13 @@
         <v>2026</v>
       </c>
       <c r="B60" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C60" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D60" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E60">
         <v>18.717144561125838</v>
@@ -7258,13 +7255,13 @@
         <v>2026</v>
       </c>
       <c r="B61" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C61" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D61" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E61">
         <v>224.09510659776549</v>
@@ -7275,13 +7272,13 @@
         <v>2026</v>
       </c>
       <c r="B62" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C62" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D62" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E62">
         <v>7.7777777777777777</v>
@@ -7292,13 +7289,13 @@
         <v>2026</v>
       </c>
       <c r="B63" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C63" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D63" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E63">
         <v>641.41370081700052</v>
@@ -7309,13 +7306,13 @@
         <v>2026</v>
       </c>
       <c r="B64" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C64" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D64" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E64">
         <v>35.873250192613433</v>
@@ -7326,13 +7323,13 @@
         <v>2030</v>
       </c>
       <c r="B65" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C65" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D65" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E65">
         <v>39.832212400033853</v>
@@ -7343,13 +7340,13 @@
         <v>2030</v>
       </c>
       <c r="B66" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C66" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D66" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E66">
         <v>0</v>
@@ -7360,13 +7357,13 @@
         <v>2030</v>
       </c>
       <c r="B67" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C67" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D67" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E67">
         <v>0</v>
@@ -7377,13 +7374,13 @@
         <v>2030</v>
       </c>
       <c r="B68" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C68" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D68" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E68">
         <v>0</v>
@@ -7394,13 +7391,13 @@
         <v>2030</v>
       </c>
       <c r="B69" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C69" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D69" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E69">
         <v>14.610653842703581</v>
@@ -7411,13 +7408,13 @@
         <v>2030</v>
       </c>
       <c r="B70" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C70" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D70" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E70">
         <v>174.92924840383711</v>
@@ -7428,13 +7425,13 @@
         <v>2030</v>
       </c>
       <c r="B71" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C71" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D71" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E71">
         <v>5.9722222222222223</v>
@@ -7445,13 +7442,13 @@
         <v>2030</v>
       </c>
       <c r="B72" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C72" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D72" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E72">
         <v>500.68927565310952</v>
@@ -7462,13 +7459,13 @@
         <v>2030</v>
       </c>
       <c r="B73" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C73" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D73" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E73">
         <v>43.97630023996615</v>
@@ -7479,13 +7476,13 @@
         <v>2035</v>
       </c>
       <c r="B74" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C74" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D74" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E74">
         <v>23.706679694440709</v>
@@ -7496,13 +7493,13 @@
         <v>2035</v>
       </c>
       <c r="B75" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C75" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D75" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E75">
         <v>0</v>
@@ -7513,13 +7510,13 @@
         <v>2035</v>
       </c>
       <c r="B76" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C76" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D76" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E76">
         <v>0</v>
@@ -7530,13 +7527,13 @@
         <v>2035</v>
       </c>
       <c r="B77" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C77" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D77" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E77">
         <v>0</v>
@@ -7547,13 +7544,13 @@
         <v>2035</v>
       </c>
       <c r="B78" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C78" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D78" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E78">
         <v>10.90299599509941</v>
@@ -7564,13 +7561,13 @@
         <v>2035</v>
       </c>
       <c r="B79" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C79" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D79" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E79">
         <v>130.53850397839989</v>
@@ -7581,13 +7578,13 @@
         <v>2035</v>
       </c>
       <c r="B80" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C80" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D80" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E80">
         <v>4.166666666666667</v>
@@ -7598,13 +7595,13 @@
         <v>2035</v>
       </c>
       <c r="B81" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C81" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D81" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E81">
         <v>373.63236621756351</v>
@@ -7615,13 +7612,13 @@
         <v>2035</v>
       </c>
       <c r="B82" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C82" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D82" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E82">
         <v>26.17308959555929</v>
@@ -7632,13 +7629,13 @@
         <v>2040</v>
       </c>
       <c r="B83" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C83" s="11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D83" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E83">
         <v>12.393484781787009</v>
@@ -7649,13 +7646,13 @@
         <v>2040</v>
       </c>
       <c r="B84" s="11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C84" s="11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D84" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E84">
         <v>0</v>
@@ -7666,13 +7663,13 @@
         <v>2040</v>
       </c>
       <c r="B85" s="11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C85" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D85" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E85">
         <v>0</v>
@@ -7683,13 +7680,13 @@
         <v>2040</v>
       </c>
       <c r="B86" s="11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C86" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D86" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E86">
         <v>0</v>
@@ -7700,13 +7697,13 @@
         <v>2040</v>
       </c>
       <c r="B87" s="11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C87" s="11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D87" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E87">
         <v>7.5610706908851792</v>
@@ -7717,13 +7714,13 @@
         <v>2040</v>
       </c>
       <c r="B88" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C88" s="11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D88" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E88">
         <v>90.526572412455437</v>
@@ -7734,13 +7731,13 @@
         <v>2040</v>
       </c>
       <c r="B89" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C89" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D89" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E89">
         <v>4.166666666666667</v>
@@ -7751,13 +7748,13 @@
         <v>2040</v>
       </c>
       <c r="B90" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C90" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D90" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E90">
         <v>259.10866468661311</v>
@@ -7768,13 +7765,13 @@
         <v>2040</v>
       </c>
       <c r="B91" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C91" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D91" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E91">
         <v>13.682885658212991</v>
@@ -7785,13 +7782,13 @@
         <v>2045</v>
       </c>
       <c r="B92" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C92" s="11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D92" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E92">
         <v>8.5006597557527961</v>
@@ -7802,13 +7799,13 @@
         <v>2045</v>
       </c>
       <c r="B93" s="11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C93" s="11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D93" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E93">
         <v>0</v>
@@ -7819,13 +7816,13 @@
         <v>2045</v>
       </c>
       <c r="B94" s="11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C94" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D94" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E94">
         <v>0</v>
@@ -7836,13 +7833,13 @@
         <v>2045</v>
       </c>
       <c r="B95" s="11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C95" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D95" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E95">
         <v>0</v>
@@ -7853,13 +7850,13 @@
         <v>2045</v>
       </c>
       <c r="B96" s="11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C96" s="11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D96" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E96">
         <v>5.6319616755606097</v>
@@ -7870,13 +7867,13 @@
         <v>2045</v>
       </c>
       <c r="B97" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C97" s="11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D97" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E97">
         <v>67.429892840629407</v>
@@ -7887,13 +7884,13 @@
         <v>2045</v>
       </c>
       <c r="B98" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C98" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D98" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E98">
         <v>4.166666666666667</v>
@@ -7904,13 +7901,13 @@
         <v>2045</v>
       </c>
       <c r="B99" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C99" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D99" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E99">
         <v>193.00045310776611</v>
@@ -7921,13 +7918,13 @@
         <v>2045</v>
       </c>
       <c r="B100" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C100" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D100" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E100">
         <v>9.3850565442472025</v>
@@ -7938,13 +7935,13 @@
         <v>2050</v>
       </c>
       <c r="B101" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C101" s="11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D101" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E101">
         <v>5.2945372674418714</v>
@@ -7955,13 +7952,13 @@
         <v>2050</v>
       </c>
       <c r="B102" s="11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C102" s="11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D102" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E102">
         <v>0</v>
@@ -7972,13 +7969,13 @@
         <v>2050</v>
       </c>
       <c r="B103" s="11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C103" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D103" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E103">
         <v>0</v>
@@ -7989,13 +7986,13 @@
         <v>2050</v>
       </c>
       <c r="B104" s="11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C104" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D104" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E104">
         <v>0</v>
@@ -8006,13 +8003,13 @@
         <v>2050</v>
       </c>
       <c r="B105" s="11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C105" s="11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D105" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E105">
         <v>5.4810375941911236</v>
@@ -8023,13 +8020,13 @@
         <v>2050</v>
       </c>
       <c r="B106" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C106" s="11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D106" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E106">
         <v>65.622921270141603</v>
@@ -8040,13 +8037,13 @@
         <v>2050</v>
       </c>
       <c r="B107" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C107" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D107" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E107">
         <v>4.166666666666667</v>
@@ -8057,13 +8054,13 @@
         <v>2050</v>
       </c>
       <c r="B108" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C108" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D108" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E108">
         <v>187.8284690341556</v>
@@ -8074,13 +8071,13 @@
         <v>2050</v>
       </c>
       <c r="B109" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C109" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D109" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E109">
         <v>5.8453735425581277</v>
@@ -8091,13 +8088,13 @@
         <v>2026</v>
       </c>
       <c r="B110" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C110" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D110" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E110">
         <v>1.004259139674806</v>
@@ -8108,13 +8105,13 @@
         <v>2026</v>
       </c>
       <c r="B111" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C111" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D111" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E111">
         <v>0</v>
@@ -8125,13 +8122,13 @@
         <v>2026</v>
       </c>
       <c r="B112" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C112" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D112" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E112">
         <v>0</v>
@@ -8142,13 +8139,13 @@
         <v>2026</v>
       </c>
       <c r="B113" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C113" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D113" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E113">
         <v>0</v>
@@ -8159,13 +8156,13 @@
         <v>2026</v>
       </c>
       <c r="B114" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C114" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D114" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E114">
         <v>0.78632377625652949</v>
@@ -8176,13 +8173,13 @@
         <v>2026</v>
       </c>
       <c r="B115" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C115" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D115" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E115">
         <v>9.4144333760472563</v>
@@ -8193,13 +8190,13 @@
         <v>2026</v>
       </c>
       <c r="B116" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C116" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D116" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E116">
         <v>1.1111111111111109</v>
@@ -8210,13 +8207,13 @@
         <v>2026</v>
       </c>
       <c r="B117" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C117" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D117" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E117">
         <v>26.946356145403541</v>
@@ -8227,13 +8224,13 @@
         <v>2026</v>
       </c>
       <c r="B118" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C118" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D118" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E118">
         <v>1.108740860325194</v>
@@ -8244,13 +8241,13 @@
         <v>2030</v>
       </c>
       <c r="B119" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C119" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D119" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E119">
         <v>0.60312581554535216</v>
@@ -8261,13 +8258,13 @@
         <v>2030</v>
       </c>
       <c r="B120" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C120" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D120" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E120">
         <v>0</v>
@@ -8278,13 +8275,13 @@
         <v>2030</v>
       </c>
       <c r="B121" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C121" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D121" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E121">
         <v>0</v>
@@ -8295,13 +8292,13 @@
         <v>2030</v>
       </c>
       <c r="B122" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C122" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D122" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E122">
         <v>0</v>
@@ -8312,13 +8309,13 @@
         <v>2030</v>
       </c>
       <c r="B123" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C123" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D123" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E123">
         <v>1.4844705073478279</v>
@@ -8329,13 +8326,13 @@
         <v>2030</v>
       </c>
       <c r="B124" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C124" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D124" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E124">
         <v>17.773147795004309</v>
@@ -8346,13 +8343,13 @@
         <v>2030</v>
       </c>
       <c r="B125" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C125" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D125" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E125">
         <v>2.2222222222222219</v>
@@ -8363,13 +8360,13 @@
         <v>2030</v>
       </c>
       <c r="B126" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C126" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D126" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E126">
         <v>50.870992568451292</v>
@@ -8380,13 +8377,13 @@
         <v>2030</v>
       </c>
       <c r="B127" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C127" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D127" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E127">
         <v>0.66587418445464774</v>
@@ -8397,13 +8394,13 @@
         <v>2035</v>
       </c>
       <c r="B128" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C128" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D128" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E128">
         <v>0.93059128986430217</v>
@@ -8414,13 +8411,13 @@
         <v>2035</v>
       </c>
       <c r="B129" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C129" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D129" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E129">
         <v>0</v>
@@ -8431,13 +8428,13 @@
         <v>2035</v>
       </c>
       <c r="B130" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C130" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D130" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E130">
         <v>0</v>
@@ -8448,13 +8445,13 @@
         <v>2035</v>
       </c>
       <c r="B131" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C131" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D131" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E131">
         <v>0</v>
@@ -8465,13 +8462,13 @@
         <v>2035</v>
       </c>
       <c r="B132" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C132" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D132" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E132">
         <v>1.470180788882288</v>
@@ -8482,13 +8479,13 @@
         <v>2035</v>
       </c>
       <c r="B133" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C133" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D133" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E133">
         <v>17.602061015590419</v>
@@ -8499,13 +8496,13 @@
         <v>2035</v>
       </c>
       <c r="B134" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C134" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D134" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E134">
         <v>3.333333333333333</v>
@@ -8516,13 +8513,13 @@
         <v>2035</v>
       </c>
       <c r="B135" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C135" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D135" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E135">
         <v>50.381301356488777</v>
@@ -8533,13 +8530,13 @@
         <v>2035</v>
       </c>
       <c r="B136" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C136" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D136" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E136">
         <v>1.0274087101356979</v>
@@ -8550,13 +8547,13 @@
         <v>2040</v>
       </c>
       <c r="B137" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C137" s="11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D137" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E137">
         <v>1.0047235227889539</v>
@@ -8567,13 +8564,13 @@
         <v>2040</v>
       </c>
       <c r="B138" s="11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C138" s="11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D138" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E138">
         <v>0</v>
@@ -8584,13 +8581,13 @@
         <v>2040</v>
       </c>
       <c r="B139" s="11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C139" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D139" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E139">
         <v>0</v>
@@ -8601,13 +8598,13 @@
         <v>2040</v>
       </c>
       <c r="B140" s="11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C140" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D140" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E140">
         <v>0</v>
@@ -8618,13 +8615,13 @@
         <v>2040</v>
       </c>
       <c r="B141" s="11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C141" s="11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D141" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E141">
         <v>0.89285945878639206</v>
@@ -8635,13 +8632,13 @@
         <v>2040</v>
       </c>
       <c r="B142" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C142" s="11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D142" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E142">
         <v>10.68995513392159</v>
@@ -8652,13 +8649,13 @@
         <v>2040</v>
       </c>
       <c r="B143" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C143" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D143" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E143">
         <v>3.8888888888888888</v>
@@ -8669,13 +8666,13 @@
         <v>2040</v>
       </c>
       <c r="B144" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C144" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D144" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E144">
         <v>30.597203964491701</v>
@@ -8686,13 +8683,13 @@
         <v>2040</v>
       </c>
       <c r="B145" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C145" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D145" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E145">
         <v>1.109253557211046</v>
@@ -8703,13 +8700,13 @@
         <v>2045</v>
       </c>
       <c r="B146" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C146" s="11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D146" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E146">
         <v>0.59763945233474225</v>
@@ -8720,13 +8717,13 @@
         <v>2045</v>
       </c>
       <c r="B147" s="11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C147" s="11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D147" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E147">
         <v>0</v>
@@ -8737,13 +8734,13 @@
         <v>2045</v>
       </c>
       <c r="B148" s="11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C148" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D148" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E148">
         <v>0</v>
@@ -8754,13 +8751,13 @@
         <v>2045</v>
       </c>
       <c r="B149" s="11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C149" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D149" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E149">
         <v>0</v>
@@ -8771,13 +8768,13 @@
         <v>2045</v>
       </c>
       <c r="B150" s="11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C150" s="11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D150" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E150">
         <v>0.43653689984869187</v>
@@ -8788,13 +8785,13 @@
         <v>2045</v>
       </c>
       <c r="B151" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C151" s="11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D151" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E151">
         <v>5.2265335017301622</v>
@@ -8805,13 +8802,13 @@
         <v>2045</v>
       </c>
       <c r="B152" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C152" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D152" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E152">
         <v>3.6111111111111112</v>
@@ -8822,13 +8819,13 @@
         <v>2045</v>
       </c>
       <c r="B153" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C153" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D153" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E153">
         <v>14.95958678743504</v>
@@ -8839,13 +8836,13 @@
         <v>2045</v>
       </c>
       <c r="B154" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C154" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D154" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E154">
         <v>0.65981702766525785</v>
@@ -8856,13 +8853,13 @@
         <v>2050</v>
       </c>
       <c r="B155" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C155" s="11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D155" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E155">
         <v>0</v>
@@ -8873,13 +8870,13 @@
         <v>2050</v>
       </c>
       <c r="B156" s="11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C156" s="11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D156" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E156">
         <v>0</v>
@@ -8890,13 +8887,13 @@
         <v>2050</v>
       </c>
       <c r="B157" s="11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C157" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D157" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E157">
         <v>0</v>
@@ -8907,13 +8904,13 @@
         <v>2050</v>
       </c>
       <c r="B158" s="11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C158" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D158" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E158">
         <v>0</v>
@@ -8924,13 +8921,13 @@
         <v>2050</v>
       </c>
       <c r="B159" s="11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C159" s="11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D159" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E159">
         <v>0.26866807811826832</v>
@@ -8941,13 +8938,13 @@
         <v>2050</v>
       </c>
       <c r="B160" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C160" s="11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D160" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E160">
         <v>3.2166873215466931</v>
@@ -8958,13 +8955,13 @@
         <v>2050</v>
       </c>
       <c r="B161" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C161" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D161" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E161">
         <v>3.333333333333333</v>
@@ -8975,13 +8972,13 @@
         <v>2050</v>
       </c>
       <c r="B162" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C162" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D162" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E162">
         <v>9.2069271418216783</v>
@@ -8992,13 +8989,13 @@
         <v>2050</v>
       </c>
       <c r="B163" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C163" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D163" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E163">
         <v>0</v>
@@ -9009,13 +9006,13 @@
         <v>2026</v>
       </c>
       <c r="B164" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C164" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D164" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E164">
         <v>164.75172986911201</v>
@@ -9026,13 +9023,13 @@
         <v>2026</v>
       </c>
       <c r="B165" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C165" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D165" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E165">
         <v>0</v>
@@ -9043,13 +9040,13 @@
         <v>2026</v>
       </c>
       <c r="B166" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C166" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D166" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E166">
         <v>0</v>
@@ -9060,13 +9057,13 @@
         <v>2026</v>
       </c>
       <c r="B167" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C167" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D167" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E167">
         <v>0</v>
@@ -9077,13 +9074,13 @@
         <v>2026</v>
       </c>
       <c r="B168" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C168" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D168" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E168">
         <v>24.141085746979751</v>
@@ -9094,13 +9091,13 @@
         <v>2026</v>
       </c>
       <c r="B169" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C169" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D169" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E169">
         <v>289.03442863240991</v>
@@ -9111,13 +9108,13 @@
         <v>2026</v>
       </c>
       <c r="B170" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C170" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D170" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E170">
         <v>3.6999999999999998E-2</v>
@@ -9128,13 +9125,13 @@
         <v>2026</v>
       </c>
       <c r="B171" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C171" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D171" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E171">
         <v>827.28554562061026</v>
@@ -9145,13 +9142,13 @@
         <v>2026</v>
       </c>
       <c r="B172" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C172" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D172" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E172">
         <v>181.89227013088811</v>
@@ -9162,13 +9159,13 @@
         <v>2030</v>
       </c>
       <c r="B173" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C173" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D173" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E173">
         <v>180.38285541545281</v>
@@ -9179,13 +9176,13 @@
         <v>2030</v>
       </c>
       <c r="B174" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C174" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D174" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E174">
         <v>0</v>
@@ -9196,13 +9193,13 @@
         <v>2030</v>
       </c>
       <c r="B175" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C175" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D175" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E175">
         <v>0</v>
@@ -9213,13 +9210,13 @@
         <v>2030</v>
       </c>
       <c r="B176" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C176" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D176" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E176">
         <v>0</v>
@@ -9230,13 +9227,13 @@
         <v>2030</v>
       </c>
       <c r="B177" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C177" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D177" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E177">
         <v>13.82385009432965</v>
@@ -9247,13 +9244,13 @@
         <v>2030</v>
       </c>
       <c r="B178" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C178" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D178" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E178">
         <v>165.5090684566469</v>
@@ -9264,13 +9261,13 @@
         <v>2030</v>
       </c>
       <c r="B179" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C179" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D179" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E179">
         <v>0</v>
@@ -9281,13 +9278,13 @@
         <v>2030</v>
       </c>
       <c r="B180" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C180" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D180" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E180">
         <v>473.72647144902339</v>
@@ -9298,13 +9295,13 @@
         <v>2030</v>
       </c>
       <c r="B181" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C181" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D181" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E181">
         <v>199.14963618454729</v>
@@ -9315,13 +9312,13 @@
         <v>2035</v>
       </c>
       <c r="B182" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C182" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D182" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E182">
         <v>140.6104754109173</v>
@@ -9332,13 +9329,13 @@
         <v>2035</v>
       </c>
       <c r="B183" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C183" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D183" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E183">
         <v>0</v>
@@ -9349,13 +9346,13 @@
         <v>2035</v>
       </c>
       <c r="B184" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C184" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D184" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E184">
         <v>0</v>
@@ -9366,13 +9363,13 @@
         <v>2035</v>
       </c>
       <c r="B185" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C185" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D185" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E185">
         <v>0</v>
@@ -9383,13 +9380,13 @@
         <v>2035</v>
       </c>
       <c r="B186" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C186" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D186" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E186">
         <v>5.6688297352257022</v>
@@ -9400,13 +9397,13 @@
         <v>2035</v>
       </c>
       <c r="B187" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C187" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D187" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E187">
         <v>67.871303747817734</v>
@@ -9417,13 +9414,13 @@
         <v>2035</v>
       </c>
       <c r="B188" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C188" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D188" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E188">
         <v>0</v>
@@ -9434,13 +9431,13 @@
         <v>2035</v>
       </c>
       <c r="B189" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C189" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D189" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E189">
         <v>194.2638765169566</v>
@@ -9451,13 +9448,13 @@
         <v>2035</v>
       </c>
       <c r="B190" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C190" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D190" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E190">
         <v>155.2393932190827</v>
@@ -9468,13 +9465,13 @@
         <v>2040</v>
       </c>
       <c r="B191" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C191" s="11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D191" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E191">
         <v>77.982331301204681</v>
@@ -9485,13 +9482,13 @@
         <v>2040</v>
       </c>
       <c r="B192" s="11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C192" s="11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D192" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E192">
         <v>0</v>
@@ -9502,13 +9499,13 @@
         <v>2040</v>
       </c>
       <c r="B193" s="11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C193" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D193" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E193">
         <v>0</v>
@@ -9519,13 +9516,13 @@
         <v>2040</v>
       </c>
       <c r="B194" s="11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C194" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D194" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E194">
         <v>0</v>
@@ -9536,13 +9533,13 @@
         <v>2040</v>
       </c>
       <c r="B195" s="11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C195" s="11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D195" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E195">
         <v>1.6380941094450781</v>
@@ -9553,13 +9550,13 @@
         <v>2040</v>
       </c>
       <c r="B196" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C196" s="11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D196" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E196">
         <v>19.612439967776059</v>
@@ -9570,13 +9567,13 @@
         <v>2040</v>
       </c>
       <c r="B197" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C197" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D197" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E197">
         <v>0</v>
@@ -9587,13 +9584,13 @@
         <v>2040</v>
       </c>
       <c r="B198" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C198" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D198" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E198">
         <v>56.135485922778869</v>
@@ -9604,13 +9601,13 @@
         <v>2040</v>
       </c>
       <c r="B199" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C199" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D199" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E199">
         <v>86.095504318795321</v>
@@ -9621,13 +9618,13 @@
         <v>2045</v>
       </c>
       <c r="B200" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C200" s="11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D200" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E200">
         <v>29.42410936394722</v>
@@ -9638,13 +9635,13 @@
         <v>2045</v>
       </c>
       <c r="B201" s="11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C201" s="11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D201" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E201">
         <v>0</v>
@@ -9655,13 +9652,13 @@
         <v>2045</v>
       </c>
       <c r="B202" s="11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C202" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D202" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E202">
         <v>0</v>
@@ -9672,13 +9669,13 @@
         <v>2045</v>
       </c>
       <c r="B203" s="11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C203" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D203" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E203">
         <v>0</v>
@@ -9689,13 +9686,13 @@
         <v>2045</v>
       </c>
       <c r="B204" s="11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C204" s="11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D204" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E204">
         <v>1.9202185232449069</v>
@@ -9706,13 +9703,13 @@
         <v>2045</v>
       </c>
       <c r="B205" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C205" s="11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D205" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E205">
         <v>22.99023621109907</v>
@@ -9723,13 +9720,13 @@
         <v>2045</v>
       </c>
       <c r="B206" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C206" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D206" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E206">
         <v>0</v>
@@ -9740,13 +9737,13 @@
         <v>2045</v>
       </c>
       <c r="B207" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C207" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D207" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E207">
         <v>65.803545265656012</v>
@@ -9757,13 +9754,13 @@
         <v>2045</v>
       </c>
       <c r="B208" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C208" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D208" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E208">
         <v>32.485352676052777</v>
@@ -9774,13 +9771,13 @@
         <v>2050</v>
       </c>
       <c r="B209" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C209" s="11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D209" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E209">
         <v>1.328835503507124</v>
@@ -9791,13 +9788,13 @@
         <v>2050</v>
       </c>
       <c r="B210" s="11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C210" s="11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D210" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E210">
         <v>0</v>
@@ -9808,13 +9805,13 @@
         <v>2050</v>
       </c>
       <c r="B211" s="11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C211" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D211" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E211">
         <v>0</v>
@@ -9825,13 +9822,13 @@
         <v>2050</v>
       </c>
       <c r="B212" s="11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C212" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D212" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E212">
         <v>0</v>
@@ -9842,13 +9839,13 @@
         <v>2050</v>
       </c>
       <c r="B213" s="11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C213" s="11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D213" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E213">
         <v>1.945821436888173</v>
@@ -9859,13 +9856,13 @@
         <v>2050</v>
       </c>
       <c r="B214" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C214" s="11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D214" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E214">
         <v>23.29677269391372</v>
@@ -9876,13 +9873,13 @@
         <v>2050</v>
       </c>
       <c r="B215" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C215" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D215" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E215">
         <v>0</v>
@@ -9893,13 +9890,13 @@
         <v>2050</v>
       </c>
       <c r="B216" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C216" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D216" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E216">
         <v>66.680925869198092</v>
@@ -9910,13 +9907,13 @@
         <v>2050</v>
       </c>
       <c r="B217" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C217" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D217" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E217">
         <v>1.4670856964928769</v>
@@ -9935,21 +9932,21 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C2">
         <v>1200</v>
@@ -9957,10 +9954,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C3">
         <v>1300</v>
@@ -9968,10 +9965,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C4">
         <v>1100</v>
@@ -9979,10 +9976,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C5">
         <v>1300</v>
@@ -9990,10 +9987,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C6">
         <v>1100</v>
@@ -10001,10 +9998,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C7">
         <v>1200</v>
@@ -10012,10 +10009,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C8">
         <v>818</v>
@@ -10023,10 +10020,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C9">
         <v>250</v>
@@ -10034,10 +10031,10 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C10">
         <v>297</v>
@@ -10048,7 +10045,7 @@
         <v>2</v>
       </c>
       <c r="B12" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
   </sheetData>
@@ -10066,24 +10063,24 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>76</v>
-      </c>
       <c r="E1" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B2">
         <v>6.2E-2</v>
@@ -10100,7 +10097,7 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B3">
         <v>3.1E-2</v>

--- a/scm_input_cleaned.xlsx
+++ b/scm_input_cleaned.xlsx
@@ -1,29 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5611d695511771a1/Desktop/Repositories/scm_model/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="525" documentId="8_{69118542-9163-4E18-BF71-86AAA6BFC266}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7A2DBF90-A9BA-4883-A216-4AFD2263B6C8}"/>
+  <xr:revisionPtr revIDLastSave="599" documentId="8_{69118542-9163-4E18-BF71-86AAA6BFC266}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7FA5C165-ABC6-4551-971D-EF91E34A1543}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="6825" windowWidth="29040" windowHeight="17520" xr2:uid="{D3628906-A666-41FC-B4DD-112A108B04C0}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="4" xr2:uid="{D3628906-A666-41FC-B4DD-112A108B04C0}"/>
   </bookViews>
   <sheets>
     <sheet name="timeseries" sheetId="1" r:id="rId1"/>
     <sheet name="sink_blocks" sheetId="2" r:id="rId2"/>
     <sheet name="economic_cc_tech" sheetId="3" r:id="rId3"/>
     <sheet name="cc_tech" sheetId="8" r:id="rId4"/>
-    <sheet name="ng_flows" sheetId="4" r:id="rId5"/>
-    <sheet name="distances" sheetId="6" r:id="rId6"/>
-    <sheet name="economic_transport" sheetId="7" r:id="rId7"/>
+    <sheet name="cc_commited_cap" sheetId="9" r:id="rId5"/>
+    <sheet name="ng_flows" sheetId="4" r:id="rId6"/>
+    <sheet name="distances" sheetId="6" r:id="rId7"/>
+    <sheet name="economic_transport" sheetId="7" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">ng_flows!$D$1:$D$217</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">sink_blocks!$A$1:$A$60</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">ng_flows!$D$1:$D$217</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">sink_blocks!$C$1:$C$60</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -250,7 +251,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1022" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1023" uniqueCount="160">
   <si>
     <t>year</t>
   </si>
@@ -516,36 +517,6 @@
     <t>ir_cap</t>
   </si>
   <si>
-    <t>3,500,000</t>
-  </si>
-  <si>
-    <t>2,500,000</t>
-  </si>
-  <si>
-    <t>2,000,000</t>
-  </si>
-  <si>
-    <t>3,000,000</t>
-  </si>
-  <si>
-    <t>8,000,000</t>
-  </si>
-  <si>
-    <t>1,000,000</t>
-  </si>
-  <si>
-    <t>500,000</t>
-  </si>
-  <si>
-    <t>1,500,000</t>
-  </si>
-  <si>
-    <t>4,000,000</t>
-  </si>
-  <si>
-    <t>6,000,000</t>
-  </si>
-  <si>
     <t>Industry_cement</t>
   </si>
   <si>
@@ -703,6 +674,63 @@
   </si>
   <si>
     <t>ENTSOE CO2 Price Trajectory</t>
+  </si>
+  <si>
+    <t>Year</t>
+  </si>
+  <si>
+    <t>EU|psc_cement</t>
+  </si>
+  <si>
+    <t>EU|psc_chemicals</t>
+  </si>
+  <si>
+    <t>EU|psc_iron_steel</t>
+  </si>
+  <si>
+    <t>EU|psc_otherindustry</t>
+  </si>
+  <si>
+    <t>EU|psc_power</t>
+  </si>
+  <si>
+    <t>EU|psc_refining</t>
+  </si>
+  <si>
+    <t>NO|psc_cement</t>
+  </si>
+  <si>
+    <t>NO|psc_chemicals</t>
+  </si>
+  <si>
+    <t>NO|psc_iron_steel</t>
+  </si>
+  <si>
+    <t>NO|psc_otherindustry</t>
+  </si>
+  <si>
+    <t>NO|psc_power</t>
+  </si>
+  <si>
+    <t>NO|psc_refining</t>
+  </si>
+  <si>
+    <t>UK|psc_cement</t>
+  </si>
+  <si>
+    <t>UK|psc_chemicals</t>
+  </si>
+  <si>
+    <t>UK|psc_iron_steel</t>
+  </si>
+  <si>
+    <t>UK|psc_otherindustry</t>
+  </si>
+  <si>
+    <t>UK|psc_power</t>
+  </si>
+  <si>
+    <t>UK|psc_refining</t>
   </si>
 </sst>
 </file>
@@ -767,7 +795,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -777,6 +805,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -796,7 +836,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -816,6 +856,12 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="3" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Komma" xfId="1" builtinId="3"/>
@@ -1272,7 +1318,7 @@
         <v>21</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>51</v>
@@ -2447,7 +2493,7 @@
         <v>8</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="F27" s="4" t="s">
         <v>10</v>
@@ -2476,7 +2522,7 @@
         <v>11</v>
       </c>
       <c r="E28" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="F28" t="s">
         <v>12</v>
@@ -2515,6 +2561,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA852480-4336-48A0-952D-1FD697CF57B6}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:O60"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2531,7 +2578,7 @@
         <v>24</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>25</v>
@@ -2570,12 +2617,12 @@
         <v>47</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>38</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="C2">
         <v>2</v>
@@ -2594,16 +2641,16 @@
         <v>207000000</v>
       </c>
       <c r="H2">
-        <v>14</v>
+        <v>2.4</v>
       </c>
       <c r="I2">
-        <v>13.44</v>
+        <v>2.4</v>
       </c>
       <c r="J2">
-        <v>12.9</v>
+        <v>2.4</v>
       </c>
       <c r="K2">
-        <v>12.39</v>
+        <v>2.4</v>
       </c>
       <c r="L2">
         <v>6</v>
@@ -2623,7 +2670,7 @@
         <v>38</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -2641,16 +2688,16 @@
         <v>2400000</v>
       </c>
       <c r="H3">
-        <v>14</v>
+        <v>2.4</v>
       </c>
       <c r="I3">
-        <v>13.44</v>
+        <v>2.4</v>
       </c>
       <c r="J3">
-        <v>12.9</v>
+        <v>2.4</v>
       </c>
       <c r="K3">
-        <v>12.39</v>
+        <v>2.4</v>
       </c>
       <c r="L3">
         <v>6</v>
@@ -2665,12 +2712,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>38</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="C4">
         <v>2</v>
@@ -2689,16 +2736,16 @@
         <v>160000000</v>
       </c>
       <c r="H4">
-        <v>14</v>
+        <v>2.4</v>
       </c>
       <c r="I4">
-        <v>13.44</v>
+        <v>2.4</v>
       </c>
       <c r="J4">
-        <v>12.9</v>
+        <v>2.4</v>
       </c>
       <c r="K4">
-        <v>12.39</v>
+        <v>2.4</v>
       </c>
       <c r="L4">
         <v>6</v>
@@ -2718,7 +2765,7 @@
         <v>38</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -2737,16 +2784,16 @@
         <v>400000000</v>
       </c>
       <c r="H5">
-        <v>14</v>
+        <v>2.4</v>
       </c>
       <c r="I5">
-        <v>13.44</v>
+        <v>2.4</v>
       </c>
       <c r="J5">
-        <v>12.9</v>
+        <v>2.4</v>
       </c>
       <c r="K5">
-        <v>12.39</v>
+        <v>2.4</v>
       </c>
       <c r="L5">
         <v>6</v>
@@ -2766,7 +2813,7 @@
         <v>38</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="C6">
         <v>1</v>
@@ -2785,16 +2832,16 @@
         <v>67000000</v>
       </c>
       <c r="H6">
-        <v>14</v>
+        <v>2.4</v>
       </c>
       <c r="I6">
-        <v>13.44</v>
+        <v>2.4</v>
       </c>
       <c r="J6">
-        <v>12.9</v>
+        <v>2.4</v>
       </c>
       <c r="K6">
-        <v>12.39</v>
+        <v>2.4</v>
       </c>
       <c r="L6">
         <v>6</v>
@@ -2814,7 +2861,7 @@
         <v>38</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="C7">
         <v>1</v>
@@ -2833,16 +2880,16 @@
         <v>43000000</v>
       </c>
       <c r="H7">
-        <v>14</v>
+        <v>2.4</v>
       </c>
       <c r="I7">
-        <v>13.44</v>
+        <v>2.4</v>
       </c>
       <c r="J7">
-        <v>12.9</v>
+        <v>2.4</v>
       </c>
       <c r="K7">
-        <v>12.39</v>
+        <v>2.4</v>
       </c>
       <c r="L7">
         <v>6</v>
@@ -2862,7 +2909,7 @@
         <v>38</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="C8">
         <v>1</v>
@@ -2881,16 +2928,16 @@
         <v>100000000</v>
       </c>
       <c r="H8">
-        <v>14</v>
+        <v>2.4</v>
       </c>
       <c r="I8">
-        <v>13.44</v>
+        <v>2.4</v>
       </c>
       <c r="J8">
-        <v>12.9</v>
+        <v>2.4</v>
       </c>
       <c r="K8">
-        <v>12.39</v>
+        <v>2.4</v>
       </c>
       <c r="L8">
         <v>6</v>
@@ -2910,7 +2957,7 @@
         <v>38</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="C9">
         <v>1</v>
@@ -2928,16 +2975,16 @@
         <v>37000000</v>
       </c>
       <c r="H9">
-        <v>14</v>
+        <v>2.4</v>
       </c>
       <c r="I9">
-        <v>13.44</v>
+        <v>2.4</v>
       </c>
       <c r="J9">
-        <v>12.9</v>
+        <v>2.4</v>
       </c>
       <c r="K9">
-        <v>12.39</v>
+        <v>2.4</v>
       </c>
       <c r="L9">
         <v>6</v>
@@ -2976,16 +3023,16 @@
         <v>50000000</v>
       </c>
       <c r="H10">
-        <v>14</v>
+        <v>2.4</v>
       </c>
       <c r="I10">
-        <v>13.44</v>
+        <v>2.4</v>
       </c>
       <c r="J10">
-        <v>12.9</v>
+        <v>2.4</v>
       </c>
       <c r="K10">
-        <v>12.39</v>
+        <v>2.4</v>
       </c>
       <c r="L10">
         <v>6</v>
@@ -3024,16 +3071,16 @@
         <v>30000000</v>
       </c>
       <c r="H11">
-        <v>14</v>
+        <v>2.4</v>
       </c>
       <c r="I11">
-        <v>13.44</v>
+        <v>2.4</v>
       </c>
       <c r="J11">
-        <v>12.9</v>
+        <v>2.4</v>
       </c>
       <c r="K11">
-        <v>12.39</v>
+        <v>2.4</v>
       </c>
       <c r="L11">
         <v>6</v>
@@ -3072,16 +3119,16 @@
         <v>20000000</v>
       </c>
       <c r="H12">
-        <v>14</v>
+        <v>2.4</v>
       </c>
       <c r="I12">
-        <v>13.44</v>
+        <v>2.4</v>
       </c>
       <c r="J12">
-        <v>12.9</v>
+        <v>2.4</v>
       </c>
       <c r="K12">
-        <v>12.39</v>
+        <v>2.4</v>
       </c>
       <c r="L12">
         <v>6</v>
@@ -3101,7 +3148,7 @@
         <v>38</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="C13">
         <v>1</v>
@@ -3119,16 +3166,16 @@
         <v>2000000</v>
       </c>
       <c r="H13">
-        <v>14</v>
+        <v>2.4</v>
       </c>
       <c r="I13">
-        <v>13.44</v>
+        <v>2.4</v>
       </c>
       <c r="J13">
-        <v>12.9</v>
+        <v>2.4</v>
       </c>
       <c r="K13">
-        <v>12.39</v>
+        <v>2.4</v>
       </c>
       <c r="L13">
         <v>6</v>
@@ -3143,12 +3190,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
         <v>38</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="C14">
         <v>2</v>
@@ -3167,16 +3214,16 @@
         <v>498000000</v>
       </c>
       <c r="H14">
-        <v>14</v>
+        <v>2.4</v>
       </c>
       <c r="I14">
-        <v>13.44</v>
+        <v>2.4</v>
       </c>
       <c r="J14">
-        <v>12.9</v>
+        <v>2.4</v>
       </c>
       <c r="K14">
-        <v>12.39</v>
+        <v>2.4</v>
       </c>
       <c r="L14">
         <v>6</v>
@@ -3196,7 +3243,7 @@
         <v>38</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="C15">
         <v>1</v>
@@ -3215,16 +3262,16 @@
         <v>32000000</v>
       </c>
       <c r="H15">
-        <v>14</v>
+        <v>2.4</v>
       </c>
       <c r="I15">
-        <v>13.44</v>
+        <v>2.4</v>
       </c>
       <c r="J15">
-        <v>12.9</v>
+        <v>2.4</v>
       </c>
       <c r="K15">
-        <v>12.39</v>
+        <v>2.4</v>
       </c>
       <c r="L15">
         <v>6</v>
@@ -3239,12 +3286,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
         <v>38</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="C16">
         <v>2</v>
@@ -3263,16 +3310,16 @@
         <v>34200000</v>
       </c>
       <c r="H16">
-        <v>14</v>
+        <v>2.4</v>
       </c>
       <c r="I16">
-        <v>13.44</v>
+        <v>2.4</v>
       </c>
       <c r="J16">
-        <v>12.9</v>
+        <v>2.4</v>
       </c>
       <c r="K16">
-        <v>12.39</v>
+        <v>2.4</v>
       </c>
       <c r="L16">
         <v>6</v>
@@ -3292,7 +3339,7 @@
         <v>38</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="C17">
         <v>1</v>
@@ -3311,16 +3358,16 @@
         <v>360000000</v>
       </c>
       <c r="H17">
-        <v>20</v>
+        <v>4.2249999999999996</v>
       </c>
       <c r="I17">
-        <v>19.2</v>
+        <v>4.2249999999999996</v>
       </c>
       <c r="J17">
-        <v>18.43</v>
+        <v>4.2249999999999996</v>
       </c>
       <c r="K17">
-        <v>17.690000000000001</v>
+        <v>4.2249999999999996</v>
       </c>
       <c r="L17">
         <v>6</v>
@@ -3340,7 +3387,7 @@
         <v>38</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="C18">
         <v>1</v>
@@ -3359,16 +3406,16 @@
         <v>250000000</v>
       </c>
       <c r="H18">
-        <v>20</v>
+        <v>4.2249999999999996</v>
       </c>
       <c r="I18">
-        <v>19.2</v>
+        <v>4.2249999999999996</v>
       </c>
       <c r="J18">
-        <v>18.43</v>
+        <v>4.2249999999999996</v>
       </c>
       <c r="K18">
-        <v>17.690000000000001</v>
+        <v>4.2249999999999996</v>
       </c>
       <c r="L18">
         <v>6</v>
@@ -3407,16 +3454,16 @@
         <v>54000000</v>
       </c>
       <c r="H19">
-        <v>20</v>
+        <v>4.2249999999999996</v>
       </c>
       <c r="I19">
-        <v>19.2</v>
+        <v>4.2249999999999996</v>
       </c>
       <c r="J19">
-        <v>18.43</v>
+        <v>4.2249999999999996</v>
       </c>
       <c r="K19">
-        <v>17.690000000000001</v>
+        <v>4.2249999999999996</v>
       </c>
       <c r="L19">
         <v>6</v>
@@ -3436,7 +3483,7 @@
         <v>38</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="C20">
         <v>1</v>
@@ -3455,16 +3502,16 @@
         <v>122999999.99999999</v>
       </c>
       <c r="H20">
-        <v>20</v>
+        <v>4.2249999999999996</v>
       </c>
       <c r="I20">
-        <v>19.2</v>
+        <v>4.2249999999999996</v>
       </c>
       <c r="J20">
-        <v>18.43</v>
+        <v>4.2249999999999996</v>
       </c>
       <c r="K20">
-        <v>17.690000000000001</v>
+        <v>4.2249999999999996</v>
       </c>
       <c r="L20">
         <v>6</v>
@@ -3503,16 +3550,16 @@
         <v>12000000</v>
       </c>
       <c r="H21">
-        <v>10</v>
+        <v>1.7</v>
       </c>
       <c r="I21">
-        <v>9.6</v>
+        <v>1.7</v>
       </c>
       <c r="J21">
-        <v>9.2200000000000006</v>
+        <v>1.7</v>
       </c>
       <c r="K21">
-        <v>8.85</v>
+        <v>1.7</v>
       </c>
       <c r="L21">
         <v>4</v>
@@ -3532,7 +3579,7 @@
         <v>38</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="C22">
         <v>1</v>
@@ -3551,16 +3598,16 @@
         <v>12000000</v>
       </c>
       <c r="H22">
-        <v>10</v>
+        <v>1.7</v>
       </c>
       <c r="I22">
-        <v>9.6</v>
+        <v>1.7</v>
       </c>
       <c r="J22">
-        <v>9.2200000000000006</v>
+        <v>1.7</v>
       </c>
       <c r="K22">
-        <v>8.85</v>
+        <v>1.7</v>
       </c>
       <c r="L22">
         <v>4</v>
@@ -3580,7 +3627,7 @@
         <v>38</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="C23">
         <v>1</v>
@@ -3599,16 +3646,16 @@
         <v>20000000</v>
       </c>
       <c r="H23">
-        <v>10</v>
+        <v>1.7</v>
       </c>
       <c r="I23">
-        <v>9.6</v>
+        <v>1.7</v>
       </c>
       <c r="J23">
-        <v>9.2200000000000006</v>
+        <v>1.7</v>
       </c>
       <c r="K23">
-        <v>8.85</v>
+        <v>1.7</v>
       </c>
       <c r="L23">
         <v>4</v>
@@ -3628,7 +3675,7 @@
         <v>38</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="C24">
         <v>1</v>
@@ -3647,16 +3694,16 @@
         <v>20000000</v>
       </c>
       <c r="H24">
-        <v>10</v>
+        <v>1.7</v>
       </c>
       <c r="I24">
-        <v>9.6</v>
+        <v>1.7</v>
       </c>
       <c r="J24">
-        <v>9.2200000000000006</v>
+        <v>1.7</v>
       </c>
       <c r="K24">
-        <v>8.85</v>
+        <v>1.7</v>
       </c>
       <c r="L24">
         <v>4</v>
@@ -3676,7 +3723,7 @@
         <v>38</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="C25">
         <v>1</v>
@@ -3695,16 +3742,16 @@
         <v>10000000</v>
       </c>
       <c r="H25">
-        <v>12</v>
+        <v>2.2250000000000001</v>
       </c>
       <c r="I25">
-        <v>11.52</v>
+        <v>2.2250000000000001</v>
       </c>
       <c r="J25">
-        <v>11.06</v>
+        <v>2.2250000000000001</v>
       </c>
       <c r="K25">
-        <v>10.62</v>
+        <v>2.2250000000000001</v>
       </c>
       <c r="L25">
         <v>4</v>
@@ -3719,12 +3766,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="8" t="s">
         <v>38</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="C26">
         <v>2</v>
@@ -3742,16 +3789,16 @@
         <v>90000000</v>
       </c>
       <c r="H26">
-        <v>12</v>
+        <v>2.2250000000000001</v>
       </c>
       <c r="I26">
-        <v>11.52</v>
+        <v>2.2250000000000001</v>
       </c>
       <c r="J26">
-        <v>11.06</v>
+        <v>2.2250000000000001</v>
       </c>
       <c r="K26">
-        <v>10.62</v>
+        <v>2.2250000000000001</v>
       </c>
       <c r="L26">
         <v>4</v>
@@ -3790,16 +3837,16 @@
         <v>15770000</v>
       </c>
       <c r="H27">
-        <v>12</v>
+        <v>2.2250000000000001</v>
       </c>
       <c r="I27">
-        <v>11.52</v>
+        <v>2.2250000000000001</v>
       </c>
       <c r="J27">
-        <v>11.06</v>
+        <v>2.2250000000000001</v>
       </c>
       <c r="K27">
-        <v>10.62</v>
+        <v>2.2250000000000001</v>
       </c>
       <c r="L27">
         <v>4</v>
@@ -3838,16 +3885,16 @@
         <v>15800000</v>
       </c>
       <c r="H28">
-        <v>12</v>
+        <v>2.2250000000000001</v>
       </c>
       <c r="I28">
-        <v>11.52</v>
+        <v>2.2250000000000001</v>
       </c>
       <c r="J28">
-        <v>11.06</v>
+        <v>2.2250000000000001</v>
       </c>
       <c r="K28">
-        <v>10.62</v>
+        <v>2.2250000000000001</v>
       </c>
       <c r="L28">
         <v>4</v>
@@ -3886,16 +3933,16 @@
         <v>5600000</v>
       </c>
       <c r="H29">
-        <v>12</v>
+        <v>2.2250000000000001</v>
       </c>
       <c r="I29">
-        <v>11.52</v>
+        <v>2.2250000000000001</v>
       </c>
       <c r="J29">
-        <v>11.06</v>
+        <v>2.2250000000000001</v>
       </c>
       <c r="K29">
-        <v>10.62</v>
+        <v>2.2250000000000001</v>
       </c>
       <c r="L29">
         <v>4</v>
@@ -3933,16 +3980,16 @@
         <v>16000000</v>
       </c>
       <c r="H30">
-        <v>12</v>
+        <v>2.2250000000000001</v>
       </c>
       <c r="I30">
-        <v>11.52</v>
+        <v>2.2250000000000001</v>
       </c>
       <c r="J30">
-        <v>11.06</v>
+        <v>2.2250000000000001</v>
       </c>
       <c r="K30">
-        <v>10.62</v>
+        <v>2.2250000000000001</v>
       </c>
       <c r="L30">
         <v>4</v>
@@ -3962,7 +4009,7 @@
         <v>29</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="C31">
         <v>1</v>
@@ -3981,16 +4028,16 @@
         <v>42750000</v>
       </c>
       <c r="H31">
-        <v>20</v>
+        <v>4.2249999999999996</v>
       </c>
       <c r="I31">
-        <v>19.2</v>
+        <v>4.2249999999999996</v>
       </c>
       <c r="J31">
-        <v>18.43</v>
+        <v>4.2249999999999996</v>
       </c>
       <c r="K31">
-        <v>17.690000000000001</v>
+        <v>4.2249999999999996</v>
       </c>
       <c r="L31">
         <v>6</v>
@@ -4005,12 +4052,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>29</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="C32">
         <v>2</v>
@@ -4029,16 +4076,16 @@
         <v>150000000</v>
       </c>
       <c r="H32">
-        <v>20</v>
+        <v>4.2249999999999996</v>
       </c>
       <c r="I32">
-        <v>19.2</v>
+        <v>4.2249999999999996</v>
       </c>
       <c r="J32">
-        <v>18.43</v>
+        <v>4.2249999999999996</v>
       </c>
       <c r="K32">
-        <v>17.690000000000001</v>
+        <v>4.2249999999999996</v>
       </c>
       <c r="L32">
         <v>6</v>
@@ -4058,7 +4105,7 @@
         <v>29</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="C33">
         <v>1</v>
@@ -4076,16 +4123,16 @@
         <v>37500000</v>
       </c>
       <c r="H33">
-        <v>20</v>
+        <v>4.2249999999999996</v>
       </c>
       <c r="I33">
-        <v>19.2</v>
+        <v>4.2249999999999996</v>
       </c>
       <c r="J33">
-        <v>18.43</v>
+        <v>4.2249999999999996</v>
       </c>
       <c r="K33">
-        <v>17.690000000000001</v>
+        <v>4.2249999999999996</v>
       </c>
       <c r="L33">
         <v>6</v>
@@ -4100,12 +4147,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>29</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="C34">
         <v>2</v>
@@ -4124,16 +4171,16 @@
         <v>87500000</v>
       </c>
       <c r="H34">
-        <v>20</v>
+        <v>4.2249999999999996</v>
       </c>
       <c r="I34">
-        <v>19.2</v>
+        <v>4.2249999999999996</v>
       </c>
       <c r="J34">
-        <v>18.43</v>
+        <v>4.2249999999999996</v>
       </c>
       <c r="K34">
-        <v>17.690000000000001</v>
+        <v>4.2249999999999996</v>
       </c>
       <c r="L34">
         <v>6</v>
@@ -4153,7 +4200,7 @@
         <v>29</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="C35">
         <v>1</v>
@@ -4172,16 +4219,16 @@
         <v>500000000</v>
       </c>
       <c r="H35">
-        <v>20</v>
+        <v>4.2249999999999996</v>
       </c>
       <c r="I35">
-        <v>19.2</v>
+        <v>4.2249999999999996</v>
       </c>
       <c r="J35">
-        <v>18.43</v>
+        <v>4.2249999999999996</v>
       </c>
       <c r="K35">
-        <v>17.690000000000001</v>
+        <v>4.2249999999999996</v>
       </c>
       <c r="L35">
         <v>6</v>
@@ -4201,7 +4248,7 @@
         <v>29</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="C36">
         <v>1</v>
@@ -4220,16 +4267,16 @@
         <v>200000000</v>
       </c>
       <c r="H36">
-        <v>20</v>
+        <v>4.2249999999999996</v>
       </c>
       <c r="I36">
-        <v>19.2</v>
+        <v>4.2249999999999996</v>
       </c>
       <c r="J36">
-        <v>18.43</v>
+        <v>4.2249999999999996</v>
       </c>
       <c r="K36">
-        <v>17.690000000000001</v>
+        <v>4.2249999999999996</v>
       </c>
       <c r="L36">
         <v>6</v>
@@ -4249,7 +4296,7 @@
         <v>29</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="C37">
         <v>1</v>
@@ -4268,16 +4315,16 @@
         <v>300000000</v>
       </c>
       <c r="H37">
-        <v>20</v>
+        <v>4.2249999999999996</v>
       </c>
       <c r="I37">
-        <v>19.2</v>
+        <v>4.2249999999999996</v>
       </c>
       <c r="J37">
-        <v>18.43</v>
+        <v>4.2249999999999996</v>
       </c>
       <c r="K37">
-        <v>17.690000000000001</v>
+        <v>4.2249999999999996</v>
       </c>
       <c r="L37">
         <v>6</v>
@@ -4297,7 +4344,7 @@
         <v>29</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="C38">
         <v>1</v>
@@ -4315,16 +4362,16 @@
         <v>100000000</v>
       </c>
       <c r="H38">
-        <v>20</v>
+        <v>4.2249999999999996</v>
       </c>
       <c r="I38">
-        <v>19.2</v>
+        <v>4.2249999999999996</v>
       </c>
       <c r="J38">
-        <v>18.43</v>
+        <v>4.2249999999999996</v>
       </c>
       <c r="K38">
-        <v>17.690000000000001</v>
+        <v>4.2249999999999996</v>
       </c>
       <c r="L38">
         <v>6</v>
@@ -4344,7 +4391,7 @@
         <v>29</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="C39">
         <v>1</v>
@@ -4363,16 +4410,16 @@
         <v>120000000</v>
       </c>
       <c r="H39">
-        <v>20</v>
+        <v>4.2249999999999996</v>
       </c>
       <c r="I39">
-        <v>19.2</v>
+        <v>4.2249999999999996</v>
       </c>
       <c r="J39">
-        <v>18.43</v>
+        <v>4.2249999999999996</v>
       </c>
       <c r="K39">
-        <v>17.690000000000001</v>
+        <v>4.2249999999999996</v>
       </c>
       <c r="L39">
         <v>6</v>
@@ -4392,7 +4439,7 @@
         <v>30</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="C40">
         <v>1</v>
@@ -4411,16 +4458,16 @@
         <v>330000000</v>
       </c>
       <c r="H40">
-        <v>14</v>
+        <v>2.4</v>
       </c>
       <c r="I40">
-        <v>13.44</v>
+        <v>2.4</v>
       </c>
       <c r="J40">
-        <v>12.9</v>
+        <v>2.4</v>
       </c>
       <c r="K40">
-        <v>12.39</v>
+        <v>2.4</v>
       </c>
       <c r="L40">
         <v>6</v>
@@ -4440,7 +4487,7 @@
         <v>30</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="C41">
         <v>1</v>
@@ -4459,16 +4506,16 @@
         <v>150000000</v>
       </c>
       <c r="H41">
-        <v>14</v>
+        <v>2.4</v>
       </c>
       <c r="I41">
-        <v>13.44</v>
+        <v>2.4</v>
       </c>
       <c r="J41">
-        <v>12.9</v>
+        <v>2.4</v>
       </c>
       <c r="K41">
-        <v>12.39</v>
+        <v>2.4</v>
       </c>
       <c r="L41">
         <v>6</v>
@@ -4488,7 +4535,7 @@
         <v>30</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="C42">
         <v>1</v>
@@ -4507,16 +4554,16 @@
         <v>135000000</v>
       </c>
       <c r="H42">
-        <v>14</v>
+        <v>2.4</v>
       </c>
       <c r="I42">
-        <v>13.44</v>
+        <v>2.4</v>
       </c>
       <c r="J42">
-        <v>12.9</v>
+        <v>2.4</v>
       </c>
       <c r="K42">
-        <v>12.39</v>
+        <v>2.4</v>
       </c>
       <c r="L42">
         <v>6</v>
@@ -4531,12 +4578,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>30</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="C43">
         <v>2</v>
@@ -4555,16 +4602,16 @@
         <v>55000000</v>
       </c>
       <c r="H43">
-        <v>14</v>
+        <v>2.4</v>
       </c>
       <c r="I43">
-        <v>13.44</v>
+        <v>2.4</v>
       </c>
       <c r="J43">
-        <v>12.9</v>
+        <v>2.4</v>
       </c>
       <c r="K43">
-        <v>12.39</v>
+        <v>2.4</v>
       </c>
       <c r="L43">
         <v>6</v>
@@ -4584,7 +4631,7 @@
         <v>30</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="C44">
         <v>1</v>
@@ -4603,16 +4650,16 @@
         <v>72000000</v>
       </c>
       <c r="H44">
-        <v>14</v>
+        <v>2.4</v>
       </c>
       <c r="I44">
-        <v>13.44</v>
+        <v>2.4</v>
       </c>
       <c r="J44">
-        <v>12.9</v>
+        <v>2.4</v>
       </c>
       <c r="K44">
-        <v>12.39</v>
+        <v>2.4</v>
       </c>
       <c r="L44">
         <v>6</v>
@@ -4627,12 +4674,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>30</v>
       </c>
       <c r="B45" s="8" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="C45">
         <v>2</v>
@@ -4651,16 +4698,16 @@
         <v>128000000</v>
       </c>
       <c r="H45">
-        <v>14</v>
+        <v>2.4</v>
       </c>
       <c r="I45">
-        <v>13.44</v>
+        <v>2.4</v>
       </c>
       <c r="J45">
-        <v>12.9</v>
+        <v>2.4</v>
       </c>
       <c r="K45">
-        <v>12.39</v>
+        <v>2.4</v>
       </c>
       <c r="L45">
         <v>6</v>
@@ -4675,12 +4722,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>30</v>
       </c>
       <c r="B46" s="8" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="C46">
         <v>3</v>
@@ -4699,16 +4746,16 @@
         <v>100000000</v>
       </c>
       <c r="H46">
-        <v>14</v>
+        <v>2.4</v>
       </c>
       <c r="I46">
-        <v>13.44</v>
+        <v>2.4</v>
       </c>
       <c r="J46">
-        <v>12.9</v>
+        <v>2.4</v>
       </c>
       <c r="K46">
-        <v>12.39</v>
+        <v>2.4</v>
       </c>
       <c r="L46">
         <v>6</v>
@@ -4728,7 +4775,7 @@
         <v>30</v>
       </c>
       <c r="B47" s="8" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="C47">
         <v>1</v>
@@ -4747,16 +4794,16 @@
         <v>100000000</v>
       </c>
       <c r="H47">
-        <v>14</v>
+        <v>2.4</v>
       </c>
       <c r="I47">
-        <v>13.44</v>
+        <v>2.4</v>
       </c>
       <c r="J47">
-        <v>12.9</v>
+        <v>2.4</v>
       </c>
       <c r="K47">
-        <v>12.39</v>
+        <v>2.4</v>
       </c>
       <c r="L47">
         <v>6</v>
@@ -4776,7 +4823,7 @@
         <v>30</v>
       </c>
       <c r="B48" s="8" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="C48">
         <v>1</v>
@@ -4795,16 +4842,16 @@
         <v>1000000000</v>
       </c>
       <c r="H48">
-        <v>14</v>
+        <v>2.4</v>
       </c>
       <c r="I48">
-        <v>13.44</v>
+        <v>2.4</v>
       </c>
       <c r="J48">
-        <v>12.9</v>
+        <v>2.4</v>
       </c>
       <c r="K48">
-        <v>12.39</v>
+        <v>2.4</v>
       </c>
       <c r="L48">
         <v>6</v>
@@ -4824,7 +4871,7 @@
         <v>30</v>
       </c>
       <c r="B49" s="8" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="C49">
         <v>1</v>
@@ -4843,16 +4890,16 @@
         <v>60000000</v>
       </c>
       <c r="H49">
-        <v>14</v>
+        <v>2.4</v>
       </c>
       <c r="I49">
-        <v>13.44</v>
+        <v>2.4</v>
       </c>
       <c r="J49">
-        <v>12.9</v>
+        <v>2.4</v>
       </c>
       <c r="K49">
-        <v>12.39</v>
+        <v>2.4</v>
       </c>
       <c r="L49">
         <v>6</v>
@@ -4867,12 +4914,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>30</v>
       </c>
       <c r="B50" s="8" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="C50">
         <v>2</v>
@@ -4891,16 +4938,16 @@
         <v>297500000</v>
       </c>
       <c r="H50">
-        <v>14</v>
+        <v>2.4</v>
       </c>
       <c r="I50">
-        <v>13.44</v>
+        <v>2.4</v>
       </c>
       <c r="J50">
-        <v>12.9</v>
+        <v>2.4</v>
       </c>
       <c r="K50">
-        <v>12.39</v>
+        <v>2.4</v>
       </c>
       <c r="L50">
         <v>6</v>
@@ -4915,12 +4962,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>30</v>
       </c>
       <c r="B51" s="8" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="C51">
         <v>3</v>
@@ -4939,16 +4986,16 @@
         <v>330000000</v>
       </c>
       <c r="H51">
-        <v>14</v>
+        <v>2.4</v>
       </c>
       <c r="I51">
-        <v>13.44</v>
+        <v>2.4</v>
       </c>
       <c r="J51">
-        <v>12.9</v>
+        <v>2.4</v>
       </c>
       <c r="K51">
-        <v>12.39</v>
+        <v>2.4</v>
       </c>
       <c r="L51">
         <v>6</v>
@@ -4968,7 +5015,7 @@
         <v>30</v>
       </c>
       <c r="B52" s="8" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="C52">
         <v>1</v>
@@ -4987,16 +5034,16 @@
         <v>30000000</v>
       </c>
       <c r="H52">
-        <v>14</v>
+        <v>2.4</v>
       </c>
       <c r="I52">
-        <v>13.44</v>
+        <v>2.4</v>
       </c>
       <c r="J52">
-        <v>12.9</v>
+        <v>2.4</v>
       </c>
       <c r="K52">
-        <v>12.39</v>
+        <v>2.4</v>
       </c>
       <c r="L52">
         <v>6</v>
@@ -5011,12 +5058,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>30</v>
       </c>
       <c r="B53" s="8" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="C53">
         <v>2</v>
@@ -5034,16 +5081,16 @@
         <v>150000000</v>
       </c>
       <c r="H53">
-        <v>14</v>
+        <v>2.4</v>
       </c>
       <c r="I53">
-        <v>13.44</v>
+        <v>2.4</v>
       </c>
       <c r="J53">
-        <v>12.9</v>
+        <v>2.4</v>
       </c>
       <c r="K53">
-        <v>12.39</v>
+        <v>2.4</v>
       </c>
       <c r="L53">
         <v>6</v>
@@ -5063,7 +5110,7 @@
         <v>30</v>
       </c>
       <c r="B54" s="8" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="C54">
         <v>1</v>
@@ -5082,16 +5129,16 @@
         <v>200000000</v>
       </c>
       <c r="H54">
-        <v>20</v>
+        <v>2.4</v>
       </c>
       <c r="I54">
-        <v>19.2</v>
+        <v>2.4</v>
       </c>
       <c r="J54">
-        <v>18.43</v>
+        <v>2.4</v>
       </c>
       <c r="K54">
-        <v>17.690000000000001</v>
+        <v>2.4</v>
       </c>
       <c r="L54">
         <v>6</v>
@@ -5111,7 +5158,7 @@
         <v>30</v>
       </c>
       <c r="B55" s="8" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="C55">
         <v>1</v>
@@ -5130,16 +5177,16 @@
         <v>90000000</v>
       </c>
       <c r="H55">
-        <v>20</v>
+        <v>4.2249999999999996</v>
       </c>
       <c r="I55">
-        <v>19.2</v>
+        <v>4.2249999999999996</v>
       </c>
       <c r="J55">
-        <v>18.43</v>
+        <v>4.2249999999999996</v>
       </c>
       <c r="K55">
-        <v>17.690000000000001</v>
+        <v>4.2249999999999996</v>
       </c>
       <c r="L55">
         <v>6</v>
@@ -5159,7 +5206,7 @@
         <v>30</v>
       </c>
       <c r="B56" s="8" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="C56">
         <v>1</v>
@@ -5178,16 +5225,16 @@
         <v>90000000</v>
       </c>
       <c r="H56">
-        <v>20</v>
+        <v>4.2249999999999996</v>
       </c>
       <c r="I56">
-        <v>19.2</v>
+        <v>4.2249999999999996</v>
       </c>
       <c r="J56">
-        <v>18.43</v>
+        <v>4.2249999999999996</v>
       </c>
       <c r="K56">
-        <v>17.690000000000001</v>
+        <v>4.2249999999999996</v>
       </c>
       <c r="L56">
         <v>6</v>
@@ -5207,7 +5254,7 @@
         <v>30</v>
       </c>
       <c r="B57" s="8" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="C57">
         <v>1</v>
@@ -5226,16 +5273,16 @@
         <v>100000000</v>
       </c>
       <c r="H57">
-        <v>20</v>
+        <v>4.2249999999999996</v>
       </c>
       <c r="I57">
-        <v>19.2</v>
+        <v>4.2249999999999996</v>
       </c>
       <c r="J57">
-        <v>18.43</v>
+        <v>4.2249999999999996</v>
       </c>
       <c r="K57">
-        <v>17.690000000000001</v>
+        <v>4.2249999999999996</v>
       </c>
       <c r="L57">
         <v>6</v>
@@ -5250,12 +5297,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>30</v>
       </c>
       <c r="B58" s="8" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="C58">
         <v>2</v>
@@ -5273,16 +5320,16 @@
         <v>150000000</v>
       </c>
       <c r="H58">
-        <v>20</v>
+        <v>4.2249999999999996</v>
       </c>
       <c r="I58">
-        <v>19.2</v>
+        <v>4.2249999999999996</v>
       </c>
       <c r="J58">
-        <v>18.43</v>
+        <v>4.2249999999999996</v>
       </c>
       <c r="K58">
-        <v>17.690000000000001</v>
+        <v>4.2249999999999996</v>
       </c>
       <c r="L58">
         <v>6</v>
@@ -5302,7 +5349,7 @@
         <v>30</v>
       </c>
       <c r="B59" s="8" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="C59">
         <v>1</v>
@@ -5321,16 +5368,16 @@
         <v>80000000</v>
       </c>
       <c r="H59">
-        <v>20</v>
+        <v>4.2249999999999996</v>
       </c>
       <c r="I59">
-        <v>19.2</v>
+        <v>4.2249999999999996</v>
       </c>
       <c r="J59">
-        <v>18.43</v>
+        <v>4.2249999999999996</v>
       </c>
       <c r="K59">
-        <v>17.690000000000001</v>
+        <v>4.2249999999999996</v>
       </c>
       <c r="L59">
         <v>6</v>
@@ -5345,12 +5392,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>30</v>
       </c>
       <c r="B60" s="8" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="C60">
         <v>2</v>
@@ -5369,16 +5416,16 @@
         <v>285000000</v>
       </c>
       <c r="H60">
-        <v>20</v>
+        <v>4.2249999999999996</v>
       </c>
       <c r="I60">
-        <v>19.2</v>
+        <v>4.2249999999999996</v>
       </c>
       <c r="J60">
-        <v>18.43</v>
+        <v>4.2249999999999996</v>
       </c>
       <c r="K60">
-        <v>17.690000000000001</v>
+        <v>4.2249999999999996</v>
       </c>
       <c r="L60">
         <v>6</v>
@@ -5394,6 +5441,13 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="C1:C60" xr:uid="{EA852480-4336-48A0-952D-1FD697CF57B6}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="1"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -5406,6 +5460,7 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
+    <col min="2" max="2" width="20.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">
@@ -5431,16 +5486,16 @@
         <v>50</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>58</v>
@@ -5452,21 +5507,21 @@
         <v>60</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="B2" t="s">
         <v>61</v>
@@ -5475,31 +5530,27 @@
         <v>57</v>
       </c>
       <c r="D2" s="6">
-        <v>143</v>
+        <v>370.07860257398664</v>
       </c>
       <c r="E2" s="6">
-        <v>131</v>
+        <v>345.55532168052969</v>
       </c>
       <c r="F2" s="6">
-        <v>111</v>
+        <v>292.04998154935089</v>
       </c>
       <c r="G2" s="6">
-        <v>95</v>
+        <v>246.34750352063568</v>
       </c>
       <c r="H2" s="6">
-        <f t="shared" ref="H2:K6" si="0">D2*0.06</f>
         <v>8.58</v>
       </c>
       <c r="I2" s="6">
-        <f t="shared" si="0"/>
         <v>7.8599999999999994</v>
       </c>
       <c r="J2" s="6">
-        <f t="shared" si="0"/>
         <v>6.66</v>
       </c>
       <c r="K2" s="6">
-        <f t="shared" si="0"/>
         <v>5.7</v>
       </c>
       <c r="L2" s="6">
@@ -5512,21 +5563,21 @@
         <v>77.5</v>
       </c>
       <c r="O2" s="6">
-        <v>40.520000000000003</v>
+        <v>36.36</v>
       </c>
       <c r="P2" s="6">
-        <v>40.520000000000003</v>
+        <v>36.36</v>
       </c>
       <c r="Q2" s="6">
-        <v>40.520000000000003</v>
+        <v>36.36</v>
       </c>
       <c r="R2" s="6">
-        <v>40.520000000000003</v>
+        <v>36.36</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="B3" t="s">
         <v>62</v>
@@ -5535,31 +5586,27 @@
         <v>57</v>
       </c>
       <c r="D3" s="6">
-        <v>105</v>
+        <v>1047.8129109022511</v>
       </c>
       <c r="E3" s="6">
-        <v>100.8</v>
+        <v>978.70184656614526</v>
       </c>
       <c r="F3" s="6">
-        <v>92.4</v>
+        <v>824.87399368900628</v>
       </c>
       <c r="G3" s="6">
-        <v>84</v>
+        <v>695.5694217053242</v>
       </c>
       <c r="H3" s="6">
-        <f t="shared" si="0"/>
         <v>6.3</v>
       </c>
       <c r="I3" s="6">
-        <f t="shared" si="0"/>
         <v>6.048</v>
       </c>
       <c r="J3" s="6">
-        <f t="shared" si="0"/>
         <v>5.5440000000000005</v>
       </c>
       <c r="K3" s="6">
-        <f t="shared" si="0"/>
         <v>5.04</v>
       </c>
       <c r="L3" s="6">
@@ -5572,21 +5619,21 @@
         <v>92</v>
       </c>
       <c r="O3" s="6">
-        <v>40.520000000000003</v>
+        <v>38.36</v>
       </c>
       <c r="P3" s="6">
-        <v>40.520000000000003</v>
+        <v>38.36</v>
       </c>
       <c r="Q3" s="6">
-        <v>40.520000000000003</v>
+        <v>38.36</v>
       </c>
       <c r="R3" s="6">
-        <v>40.520000000000003</v>
+        <v>38.36</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="B4" t="s">
         <v>63</v>
@@ -5595,31 +5642,27 @@
         <v>57</v>
       </c>
       <c r="D4" s="6">
-        <v>36</v>
+        <v>339.98184875019854</v>
       </c>
       <c r="E4" s="6">
-        <v>34.6</v>
+        <v>317.68795702887405</v>
       </c>
       <c r="F4" s="6">
-        <v>31.7</v>
+        <v>267.52670065589393</v>
       </c>
       <c r="G4" s="6">
-        <v>28.8</v>
+        <v>226.28300097144361</v>
       </c>
       <c r="H4" s="6">
-        <f t="shared" si="0"/>
         <v>2.16</v>
       </c>
       <c r="I4" s="6">
-        <f t="shared" si="0"/>
         <v>2.0760000000000001</v>
       </c>
       <c r="J4" s="6">
-        <f t="shared" si="0"/>
         <v>1.9019999999999999</v>
       </c>
       <c r="K4" s="6">
-        <f t="shared" si="0"/>
         <v>1.728</v>
       </c>
       <c r="L4" s="6">
@@ -5632,21 +5675,21 @@
         <v>94.5</v>
       </c>
       <c r="O4" s="6">
-        <v>40.520000000000003</v>
+        <v>37.28</v>
       </c>
       <c r="P4" s="6">
-        <v>40.520000000000003</v>
+        <v>37.28</v>
       </c>
       <c r="Q4" s="6">
-        <v>40.520000000000003</v>
+        <v>37.28</v>
       </c>
       <c r="R4" s="6">
-        <v>40.520000000000003</v>
+        <v>37.28</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="B5" t="s">
         <v>64</v>
@@ -5655,31 +5698,27 @@
         <v>57</v>
       </c>
       <c r="D5" s="6">
-        <v>105</v>
+        <v>836.02093954966858</v>
       </c>
       <c r="E5" s="6">
-        <v>100.8</v>
+        <v>780.28621024635731</v>
       </c>
       <c r="F5" s="6">
-        <v>92.4</v>
+        <v>657.66980577907259</v>
       </c>
       <c r="G5" s="6">
-        <v>84</v>
+        <v>555.11790386097982</v>
       </c>
       <c r="H5" s="6">
-        <f t="shared" si="0"/>
         <v>6.3</v>
       </c>
       <c r="I5" s="6">
-        <f t="shared" si="0"/>
         <v>6.048</v>
       </c>
       <c r="J5" s="6">
-        <f t="shared" si="0"/>
         <v>5.5440000000000005</v>
       </c>
       <c r="K5" s="6">
-        <f t="shared" si="0"/>
         <v>5.04</v>
       </c>
       <c r="L5" s="6">
@@ -5692,16 +5731,16 @@
         <v>94.5</v>
       </c>
       <c r="O5" s="6">
-        <v>40.520000000000003</v>
+        <v>35.1</v>
       </c>
       <c r="P5" s="6">
-        <v>40.520000000000003</v>
+        <v>35.1</v>
       </c>
       <c r="Q5" s="6">
-        <v>40.520000000000003</v>
+        <v>35.1</v>
       </c>
       <c r="R5" s="6">
-        <v>40.520000000000003</v>
+        <v>35.1</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
@@ -5715,34 +5754,27 @@
         <v>57</v>
       </c>
       <c r="D6" s="6">
-        <v>85</v>
+        <v>947.49039815629101</v>
       </c>
       <c r="E6" s="6">
-        <f>D6*(1-0.075)</f>
-        <v>78.625</v>
+        <v>876.42861829456922</v>
       </c>
       <c r="F6" s="6">
-        <f>E6-(1-0.075)</f>
-        <v>77.7</v>
+        <v>866.11769337345663</v>
       </c>
       <c r="G6" s="6">
-        <f>F6-(1-0.075)</f>
-        <v>76.775000000000006</v>
+        <v>855.80676845234404</v>
       </c>
       <c r="H6" s="6">
-        <f t="shared" si="0"/>
         <v>5.0999999999999996</v>
       </c>
       <c r="I6" s="6">
-        <f t="shared" si="0"/>
         <v>4.7175000000000002</v>
       </c>
       <c r="J6" s="6">
-        <f t="shared" si="0"/>
         <v>4.6619999999999999</v>
       </c>
       <c r="K6" s="6">
-        <f t="shared" si="0"/>
         <v>4.6065000000000005</v>
       </c>
       <c r="L6" s="6">
@@ -5769,41 +5801,37 @@
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="B7" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="C7" t="s">
         <v>57</v>
       </c>
       <c r="D7" s="6">
-        <v>143</v>
+        <v>1047.8129109022511</v>
       </c>
       <c r="E7" s="6">
-        <v>131</v>
+        <v>978.70184656614526</v>
       </c>
       <c r="F7" s="6">
-        <v>111</v>
+        <v>824.87399368900628</v>
       </c>
       <c r="G7" s="6">
-        <v>95</v>
+        <v>695.5694217053242</v>
       </c>
       <c r="H7" s="6">
-        <f t="shared" ref="H7" si="1">D7*0.06</f>
-        <v>8.58</v>
+        <v>6.3</v>
       </c>
       <c r="I7" s="6">
-        <f t="shared" ref="I7" si="2">E7*0.06</f>
-        <v>7.8599999999999994</v>
+        <v>6.048</v>
       </c>
       <c r="J7" s="6">
-        <f t="shared" ref="J7" si="3">F7*0.06</f>
-        <v>6.66</v>
+        <v>5.5440000000000005</v>
       </c>
       <c r="K7" s="6">
-        <f t="shared" ref="K7" si="4">G7*0.06</f>
-        <v>5.7</v>
+        <v>5.04</v>
       </c>
       <c r="L7" s="6">
         <v>65</v>
@@ -5863,7 +5891,7 @@
         <v>38</v>
       </c>
       <c r="B2" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="C2" t="s">
         <v>61</v>
@@ -5871,11 +5899,11 @@
       <c r="D2">
         <v>0</v>
       </c>
-      <c r="E2" t="s">
-        <v>88</v>
+      <c r="E2">
+        <v>7650000</v>
       </c>
       <c r="F2">
-        <v>0.8</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -5883,19 +5911,19 @@
         <v>38</v>
       </c>
       <c r="B3" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="C3" t="s">
         <v>62</v>
       </c>
-      <c r="D3">
-        <v>0</v>
-      </c>
-      <c r="E3" t="s">
-        <v>89</v>
+      <c r="D3" s="15">
+        <v>125000</v>
+      </c>
+      <c r="E3">
+        <v>112000</v>
       </c>
       <c r="F3">
-        <v>1</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -5903,7 +5931,7 @@
         <v>38</v>
       </c>
       <c r="B4" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="C4" t="s">
         <v>63</v>
@@ -5911,11 +5939,11 @@
       <c r="D4">
         <v>0</v>
       </c>
-      <c r="E4" t="s">
-        <v>90</v>
+      <c r="E4">
+        <v>2610000</v>
       </c>
       <c r="F4">
-        <v>0.75</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -5923,19 +5951,19 @@
         <v>38</v>
       </c>
       <c r="B5" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="C5" t="s">
         <v>64</v>
       </c>
-      <c r="D5">
-        <v>160000</v>
-      </c>
-      <c r="E5" t="s">
-        <v>91</v>
+      <c r="D5" s="14">
+        <v>910000</v>
+      </c>
+      <c r="E5">
+        <v>5400000</v>
       </c>
       <c r="F5">
-        <v>0.5</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -5948,14 +5976,14 @@
       <c r="C6" t="s">
         <v>65</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="15">
         <v>100000</v>
       </c>
-      <c r="E6" t="s">
-        <v>92</v>
+      <c r="E6">
+        <v>12950000</v>
       </c>
       <c r="F6">
-        <v>1.5</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -5963,19 +5991,19 @@
         <v>29</v>
       </c>
       <c r="B7" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="C7" t="s">
         <v>61</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="13">
         <v>400000</v>
       </c>
-      <c r="E7" t="s">
-        <v>93</v>
+      <c r="E7">
+        <v>400000</v>
       </c>
       <c r="F7">
-        <v>0.4</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -5983,7 +6011,7 @@
         <v>29</v>
       </c>
       <c r="B8" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="C8" t="s">
         <v>62</v>
@@ -5991,11 +6019,11 @@
       <c r="D8">
         <v>0</v>
       </c>
-      <c r="E8" t="s">
-        <v>94</v>
+      <c r="E8">
+        <v>260000</v>
       </c>
       <c r="F8">
-        <v>0.5</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -6003,7 +6031,7 @@
         <v>29</v>
       </c>
       <c r="B9" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="C9" t="s">
         <v>63</v>
@@ -6011,11 +6039,11 @@
       <c r="D9">
         <v>0</v>
       </c>
-      <c r="E9" t="s">
-        <v>94</v>
+      <c r="E9">
+        <v>200000</v>
       </c>
       <c r="F9">
-        <v>0.5</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -6023,7 +6051,7 @@
         <v>29</v>
       </c>
       <c r="B10" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="C10" t="s">
         <v>64</v>
@@ -6031,11 +6059,11 @@
       <c r="D10">
         <v>1700000</v>
       </c>
-      <c r="E10" t="s">
-        <v>90</v>
+      <c r="E10">
+        <v>500000</v>
       </c>
       <c r="F10">
-        <v>0.3</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -6051,11 +6079,11 @@
       <c r="D11">
         <v>0</v>
       </c>
-      <c r="E11" t="s">
-        <v>94</v>
+      <c r="E11">
+        <v>450000</v>
       </c>
       <c r="F11">
-        <v>0.6</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -6063,7 +6091,7 @@
         <v>30</v>
       </c>
       <c r="B12" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="C12" t="s">
         <v>61</v>
@@ -6071,11 +6099,11 @@
       <c r="D12">
         <v>0</v>
       </c>
-      <c r="E12" t="s">
-        <v>90</v>
+      <c r="E12">
+        <v>800000</v>
       </c>
       <c r="F12">
-        <v>0.8</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -6083,7 +6111,7 @@
         <v>30</v>
       </c>
       <c r="B13" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="C13" t="s">
         <v>62</v>
@@ -6091,11 +6119,11 @@
       <c r="D13">
         <v>0</v>
       </c>
-      <c r="E13" t="s">
-        <v>95</v>
+      <c r="E13">
+        <v>125000</v>
       </c>
       <c r="F13">
-        <v>1</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -6103,7 +6131,7 @@
         <v>30</v>
       </c>
       <c r="B14" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="C14" t="s">
         <v>63</v>
@@ -6111,11 +6139,11 @@
       <c r="D14">
         <v>0</v>
       </c>
-      <c r="E14" t="s">
-        <v>91</v>
+      <c r="E14">
+        <v>1000000</v>
       </c>
       <c r="F14">
-        <v>1</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -6123,7 +6151,7 @@
         <v>30</v>
       </c>
       <c r="B15" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="C15" t="s">
         <v>64</v>
@@ -6131,11 +6159,11 @@
       <c r="D15">
         <v>0</v>
       </c>
-      <c r="E15" t="s">
-        <v>96</v>
+      <c r="E15">
+        <v>1360000</v>
       </c>
       <c r="F15">
-        <v>0.9</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -6151,11 +6179,11 @@
       <c r="D16">
         <v>0</v>
       </c>
-      <c r="E16" t="s">
-        <v>97</v>
+      <c r="E16">
+        <v>10600000</v>
       </c>
       <c r="F16">
-        <v>1.2</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -6163,19 +6191,19 @@
         <v>38</v>
       </c>
       <c r="B17" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="C17" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="D17">
         <v>0</v>
       </c>
-      <c r="E17" t="s">
-        <v>95</v>
+      <c r="E17">
+        <v>6290000</v>
       </c>
       <c r="F17">
-        <v>0.5</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -6183,19 +6211,19 @@
         <v>29</v>
       </c>
       <c r="B18" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="C18" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="D18">
         <v>0</v>
       </c>
-      <c r="E18" t="s">
-        <v>94</v>
+      <c r="E18">
+        <v>2000000</v>
       </c>
       <c r="F18">
-        <v>0.5</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -6203,19 +6231,19 @@
         <v>30</v>
       </c>
       <c r="B19" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="C19" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="D19">
         <v>0</v>
       </c>
-      <c r="E19" t="s">
-        <v>95</v>
+      <c r="E19">
+        <v>11195000</v>
       </c>
       <c r="F19">
-        <v>0.5</v>
+        <v>0.02</v>
       </c>
     </row>
   </sheetData>
@@ -6226,6 +6254,1550 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5A2BEAB-012A-44FE-9D5A-F890D4AF74D1}">
+  <dimension ref="A1:S26"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>141</v>
+      </c>
+      <c r="B1" t="s">
+        <v>142</v>
+      </c>
+      <c r="C1" t="s">
+        <v>143</v>
+      </c>
+      <c r="D1" t="s">
+        <v>144</v>
+      </c>
+      <c r="E1" t="s">
+        <v>145</v>
+      </c>
+      <c r="F1" t="s">
+        <v>146</v>
+      </c>
+      <c r="G1" t="s">
+        <v>147</v>
+      </c>
+      <c r="H1" t="s">
+        <v>148</v>
+      </c>
+      <c r="I1" t="s">
+        <v>149</v>
+      </c>
+      <c r="J1" t="s">
+        <v>150</v>
+      </c>
+      <c r="K1" t="s">
+        <v>151</v>
+      </c>
+      <c r="L1" t="s">
+        <v>152</v>
+      </c>
+      <c r="M1" t="s">
+        <v>153</v>
+      </c>
+      <c r="N1" t="s">
+        <v>154</v>
+      </c>
+      <c r="O1" t="s">
+        <v>155</v>
+      </c>
+      <c r="P1" t="s">
+        <v>156</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>157</v>
+      </c>
+      <c r="R1" t="s">
+        <v>158</v>
+      </c>
+      <c r="S1" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>2026</v>
+      </c>
+      <c r="B2">
+        <v>200000</v>
+      </c>
+      <c r="C2">
+        <v>800000</v>
+      </c>
+      <c r="D2">
+        <v>125000</v>
+      </c>
+      <c r="E2">
+        <v>631000</v>
+      </c>
+      <c r="F2">
+        <v>530000</v>
+      </c>
+      <c r="G2">
+        <v>3228000</v>
+      </c>
+      <c r="H2">
+        <v>400000</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>1700000</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <v>0</v>
+      </c>
+      <c r="Q2">
+        <v>0</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2027</v>
+      </c>
+      <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="C3">
+        <v>2610000</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>1164000</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>0</v>
+      </c>
+      <c r="L3">
+        <v>100000</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>0</v>
+      </c>
+      <c r="Q3">
+        <v>0</v>
+      </c>
+      <c r="R3">
+        <v>5300000</v>
+      </c>
+      <c r="S3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>2028</v>
+      </c>
+      <c r="B4">
+        <v>2176000</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>4500000</v>
+      </c>
+      <c r="F4">
+        <v>1993000</v>
+      </c>
+      <c r="G4">
+        <v>1000000</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>260000</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
+      <c r="L4">
+        <v>100000</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>0</v>
+      </c>
+      <c r="Q4">
+        <v>3718000</v>
+      </c>
+      <c r="R4">
+        <v>10600000</v>
+      </c>
+      <c r="S4">
+        <v>1360000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>2029</v>
+      </c>
+      <c r="B5">
+        <v>7459000</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>112000</v>
+      </c>
+      <c r="E5">
+        <v>3188000</v>
+      </c>
+      <c r="F5">
+        <v>1160000</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5">
+        <v>350000</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <v>800000</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>0</v>
+      </c>
+      <c r="Q5">
+        <v>0</v>
+      </c>
+      <c r="R5">
+        <v>2270000</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>2030</v>
+      </c>
+      <c r="B6">
+        <v>7650000</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>6290000</v>
+      </c>
+      <c r="F6">
+        <v>12950000</v>
+      </c>
+      <c r="G6">
+        <v>5400000</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+      <c r="L6">
+        <v>450000</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6">
+        <v>1000000</v>
+      </c>
+      <c r="P6">
+        <v>0</v>
+      </c>
+      <c r="Q6">
+        <v>11195000</v>
+      </c>
+      <c r="R6">
+        <v>10000000</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>2031</v>
+      </c>
+      <c r="B7">
+        <v>4600000</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>1700000</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>740000</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>2000000</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>0</v>
+      </c>
+      <c r="Q7">
+        <v>0</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>2032</v>
+      </c>
+      <c r="B8">
+        <v>5415000</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>2000000</v>
+      </c>
+      <c r="F8">
+        <v>3500000</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8">
+        <v>540000</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <v>0</v>
+      </c>
+      <c r="Q8">
+        <v>890000</v>
+      </c>
+      <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>2033</v>
+      </c>
+      <c r="B9">
+        <v>600000</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9">
+        <v>0</v>
+      </c>
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9">
+        <v>0</v>
+      </c>
+      <c r="Q9">
+        <v>0</v>
+      </c>
+      <c r="R9">
+        <v>6700000</v>
+      </c>
+      <c r="S9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>2034</v>
+      </c>
+      <c r="B10">
+        <v>0</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>0</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10">
+        <v>0</v>
+      </c>
+      <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10">
+        <v>0</v>
+      </c>
+      <c r="Q10">
+        <v>0</v>
+      </c>
+      <c r="R10">
+        <v>5600000</v>
+      </c>
+      <c r="S10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A11" s="16">
+        <v>2035</v>
+      </c>
+      <c r="B11" s="16">
+        <v>0</v>
+      </c>
+      <c r="C11" s="16">
+        <v>0</v>
+      </c>
+      <c r="D11" s="16">
+        <v>0</v>
+      </c>
+      <c r="E11" s="16">
+        <v>0</v>
+      </c>
+      <c r="F11" s="16">
+        <v>0</v>
+      </c>
+      <c r="G11" s="16">
+        <v>0</v>
+      </c>
+      <c r="H11" s="16">
+        <v>0</v>
+      </c>
+      <c r="I11" s="16">
+        <v>0</v>
+      </c>
+      <c r="J11" s="16">
+        <v>0</v>
+      </c>
+      <c r="K11" s="16">
+        <v>150000</v>
+      </c>
+      <c r="L11" s="16">
+        <v>270000</v>
+      </c>
+      <c r="M11" s="16">
+        <v>0</v>
+      </c>
+      <c r="N11" s="16">
+        <v>0</v>
+      </c>
+      <c r="O11" s="16">
+        <v>0</v>
+      </c>
+      <c r="P11" s="16">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="16">
+        <v>1500000</v>
+      </c>
+      <c r="R11" s="16">
+        <v>1870000</v>
+      </c>
+      <c r="S11" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>2036</v>
+      </c>
+      <c r="B12">
+        <v>7650000</v>
+      </c>
+      <c r="C12">
+        <v>2610000</v>
+      </c>
+      <c r="D12">
+        <v>112000</v>
+      </c>
+      <c r="E12">
+        <v>6290000</v>
+      </c>
+      <c r="F12">
+        <v>12950000</v>
+      </c>
+      <c r="G12">
+        <v>5400000</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>260000</v>
+      </c>
+      <c r="K12">
+        <v>2000000</v>
+      </c>
+      <c r="L12">
+        <v>450000</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12">
+        <v>800000</v>
+      </c>
+      <c r="O12">
+        <v>1000000</v>
+      </c>
+      <c r="P12">
+        <v>0</v>
+      </c>
+      <c r="Q12">
+        <v>11195000</v>
+      </c>
+      <c r="R12">
+        <v>10600000</v>
+      </c>
+      <c r="S12">
+        <v>1360000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>2037</v>
+      </c>
+      <c r="B13">
+        <v>7650000</v>
+      </c>
+      <c r="C13">
+        <v>2610000</v>
+      </c>
+      <c r="D13">
+        <v>112000</v>
+      </c>
+      <c r="E13">
+        <v>6290000</v>
+      </c>
+      <c r="F13">
+        <v>12950000</v>
+      </c>
+      <c r="G13">
+        <v>5400000</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>260000</v>
+      </c>
+      <c r="K13">
+        <v>2000000</v>
+      </c>
+      <c r="L13">
+        <v>450000</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13">
+        <v>800000</v>
+      </c>
+      <c r="O13">
+        <v>1000000</v>
+      </c>
+      <c r="P13">
+        <v>0</v>
+      </c>
+      <c r="Q13">
+        <v>11195000</v>
+      </c>
+      <c r="R13">
+        <v>10600000</v>
+      </c>
+      <c r="S13">
+        <v>1360000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>2038</v>
+      </c>
+      <c r="B14">
+        <v>7650000</v>
+      </c>
+      <c r="C14">
+        <v>2610000</v>
+      </c>
+      <c r="D14">
+        <v>112000</v>
+      </c>
+      <c r="E14">
+        <v>6290000</v>
+      </c>
+      <c r="F14">
+        <v>12950000</v>
+      </c>
+      <c r="G14">
+        <v>5400000</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>260000</v>
+      </c>
+      <c r="K14">
+        <v>2000000</v>
+      </c>
+      <c r="L14">
+        <v>450000</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14">
+        <v>800000</v>
+      </c>
+      <c r="O14">
+        <v>1000000</v>
+      </c>
+      <c r="P14">
+        <v>0</v>
+      </c>
+      <c r="Q14">
+        <v>11195000</v>
+      </c>
+      <c r="R14">
+        <v>10600000</v>
+      </c>
+      <c r="S14">
+        <v>1360000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>2039</v>
+      </c>
+      <c r="B15">
+        <v>7650000</v>
+      </c>
+      <c r="C15">
+        <v>2610000</v>
+      </c>
+      <c r="D15">
+        <v>112000</v>
+      </c>
+      <c r="E15">
+        <v>6290000</v>
+      </c>
+      <c r="F15">
+        <v>12950000</v>
+      </c>
+      <c r="G15">
+        <v>5400000</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>260000</v>
+      </c>
+      <c r="K15">
+        <v>2000000</v>
+      </c>
+      <c r="L15">
+        <v>450000</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15">
+        <v>800000</v>
+      </c>
+      <c r="O15">
+        <v>1000000</v>
+      </c>
+      <c r="P15">
+        <v>0</v>
+      </c>
+      <c r="Q15">
+        <v>11195000</v>
+      </c>
+      <c r="R15">
+        <v>10600000</v>
+      </c>
+      <c r="S15">
+        <v>1360000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>2040</v>
+      </c>
+      <c r="B16">
+        <v>7650000</v>
+      </c>
+      <c r="C16">
+        <v>2610000</v>
+      </c>
+      <c r="D16">
+        <v>112000</v>
+      </c>
+      <c r="E16">
+        <v>6290000</v>
+      </c>
+      <c r="F16">
+        <v>12950000</v>
+      </c>
+      <c r="G16">
+        <v>5400000</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>260000</v>
+      </c>
+      <c r="K16">
+        <v>2000000</v>
+      </c>
+      <c r="L16">
+        <v>450000</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16">
+        <v>800000</v>
+      </c>
+      <c r="O16">
+        <v>1000000</v>
+      </c>
+      <c r="P16">
+        <v>0</v>
+      </c>
+      <c r="Q16">
+        <v>11195000</v>
+      </c>
+      <c r="R16">
+        <v>10600000</v>
+      </c>
+      <c r="S16">
+        <v>1360000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>2041</v>
+      </c>
+      <c r="B17">
+        <v>7650000</v>
+      </c>
+      <c r="C17">
+        <v>2610000</v>
+      </c>
+      <c r="D17">
+        <v>112000</v>
+      </c>
+      <c r="E17">
+        <v>6290000</v>
+      </c>
+      <c r="F17">
+        <v>12950000</v>
+      </c>
+      <c r="G17">
+        <v>5400000</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>260000</v>
+      </c>
+      <c r="K17">
+        <v>2000000</v>
+      </c>
+      <c r="L17">
+        <v>450000</v>
+      </c>
+      <c r="M17">
+        <v>0</v>
+      </c>
+      <c r="N17">
+        <v>800000</v>
+      </c>
+      <c r="O17">
+        <v>1000000</v>
+      </c>
+      <c r="P17">
+        <v>0</v>
+      </c>
+      <c r="Q17">
+        <v>11195000</v>
+      </c>
+      <c r="R17">
+        <v>10600000</v>
+      </c>
+      <c r="S17">
+        <v>1360000</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>2042</v>
+      </c>
+      <c r="B18">
+        <v>7650000</v>
+      </c>
+      <c r="C18">
+        <v>2610000</v>
+      </c>
+      <c r="D18">
+        <v>112000</v>
+      </c>
+      <c r="E18">
+        <v>6290000</v>
+      </c>
+      <c r="F18">
+        <v>12950000</v>
+      </c>
+      <c r="G18">
+        <v>5400000</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>260000</v>
+      </c>
+      <c r="K18">
+        <v>2000000</v>
+      </c>
+      <c r="L18">
+        <v>450000</v>
+      </c>
+      <c r="M18">
+        <v>0</v>
+      </c>
+      <c r="N18">
+        <v>800000</v>
+      </c>
+      <c r="O18">
+        <v>1000000</v>
+      </c>
+      <c r="P18">
+        <v>0</v>
+      </c>
+      <c r="Q18">
+        <v>11195000</v>
+      </c>
+      <c r="R18">
+        <v>10600000</v>
+      </c>
+      <c r="S18">
+        <v>1360000</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>2043</v>
+      </c>
+      <c r="B19">
+        <v>7650000</v>
+      </c>
+      <c r="C19">
+        <v>2610000</v>
+      </c>
+      <c r="D19">
+        <v>112000</v>
+      </c>
+      <c r="E19">
+        <v>6290000</v>
+      </c>
+      <c r="F19">
+        <v>12950000</v>
+      </c>
+      <c r="G19">
+        <v>5400000</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>260000</v>
+      </c>
+      <c r="K19">
+        <v>2000000</v>
+      </c>
+      <c r="L19">
+        <v>450000</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19">
+        <v>800000</v>
+      </c>
+      <c r="O19">
+        <v>1000000</v>
+      </c>
+      <c r="P19">
+        <v>0</v>
+      </c>
+      <c r="Q19">
+        <v>11195000</v>
+      </c>
+      <c r="R19">
+        <v>10600000</v>
+      </c>
+      <c r="S19">
+        <v>1360000</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>2044</v>
+      </c>
+      <c r="B20">
+        <v>7650000</v>
+      </c>
+      <c r="C20">
+        <v>2610000</v>
+      </c>
+      <c r="D20">
+        <v>112000</v>
+      </c>
+      <c r="E20">
+        <v>6290000</v>
+      </c>
+      <c r="F20">
+        <v>12950000</v>
+      </c>
+      <c r="G20">
+        <v>5400000</v>
+      </c>
+      <c r="H20">
+        <v>0</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>260000</v>
+      </c>
+      <c r="K20">
+        <v>2000000</v>
+      </c>
+      <c r="L20">
+        <v>450000</v>
+      </c>
+      <c r="M20">
+        <v>0</v>
+      </c>
+      <c r="N20">
+        <v>800000</v>
+      </c>
+      <c r="O20">
+        <v>1000000</v>
+      </c>
+      <c r="P20">
+        <v>0</v>
+      </c>
+      <c r="Q20">
+        <v>11195000</v>
+      </c>
+      <c r="R20">
+        <v>10600000</v>
+      </c>
+      <c r="S20">
+        <v>1360000</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>2045</v>
+      </c>
+      <c r="B21">
+        <v>7650000</v>
+      </c>
+      <c r="C21">
+        <v>2610000</v>
+      </c>
+      <c r="D21">
+        <v>112000</v>
+      </c>
+      <c r="E21">
+        <v>6290000</v>
+      </c>
+      <c r="F21">
+        <v>12950000</v>
+      </c>
+      <c r="G21">
+        <v>5400000</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>260000</v>
+      </c>
+      <c r="K21">
+        <v>2000000</v>
+      </c>
+      <c r="L21">
+        <v>450000</v>
+      </c>
+      <c r="M21">
+        <v>0</v>
+      </c>
+      <c r="N21">
+        <v>800000</v>
+      </c>
+      <c r="O21">
+        <v>1000000</v>
+      </c>
+      <c r="P21">
+        <v>0</v>
+      </c>
+      <c r="Q21">
+        <v>11195000</v>
+      </c>
+      <c r="R21">
+        <v>10600000</v>
+      </c>
+      <c r="S21">
+        <v>1360000</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>2046</v>
+      </c>
+      <c r="B22">
+        <v>7650000</v>
+      </c>
+      <c r="C22">
+        <v>2610000</v>
+      </c>
+      <c r="D22">
+        <v>112000</v>
+      </c>
+      <c r="E22">
+        <v>6290000</v>
+      </c>
+      <c r="F22">
+        <v>12950000</v>
+      </c>
+      <c r="G22">
+        <v>5400000</v>
+      </c>
+      <c r="H22">
+        <v>0</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>260000</v>
+      </c>
+      <c r="K22">
+        <v>2000000</v>
+      </c>
+      <c r="L22">
+        <v>450000</v>
+      </c>
+      <c r="M22">
+        <v>0</v>
+      </c>
+      <c r="N22">
+        <v>800000</v>
+      </c>
+      <c r="O22">
+        <v>1000000</v>
+      </c>
+      <c r="P22">
+        <v>0</v>
+      </c>
+      <c r="Q22">
+        <v>11195000</v>
+      </c>
+      <c r="R22">
+        <v>10600000</v>
+      </c>
+      <c r="S22">
+        <v>1360000</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>2047</v>
+      </c>
+      <c r="B23">
+        <v>7650000</v>
+      </c>
+      <c r="C23">
+        <v>2610000</v>
+      </c>
+      <c r="D23">
+        <v>112000</v>
+      </c>
+      <c r="E23">
+        <v>6290000</v>
+      </c>
+      <c r="F23">
+        <v>12950000</v>
+      </c>
+      <c r="G23">
+        <v>5400000</v>
+      </c>
+      <c r="H23">
+        <v>0</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>260000</v>
+      </c>
+      <c r="K23">
+        <v>2000000</v>
+      </c>
+      <c r="L23">
+        <v>450000</v>
+      </c>
+      <c r="M23">
+        <v>0</v>
+      </c>
+      <c r="N23">
+        <v>800000</v>
+      </c>
+      <c r="O23">
+        <v>1000000</v>
+      </c>
+      <c r="P23">
+        <v>0</v>
+      </c>
+      <c r="Q23">
+        <v>11195000</v>
+      </c>
+      <c r="R23">
+        <v>10600000</v>
+      </c>
+      <c r="S23">
+        <v>1360000</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>2048</v>
+      </c>
+      <c r="B24">
+        <v>7650000</v>
+      </c>
+      <c r="C24">
+        <v>2610000</v>
+      </c>
+      <c r="D24">
+        <v>112000</v>
+      </c>
+      <c r="E24">
+        <v>6290000</v>
+      </c>
+      <c r="F24">
+        <v>12950000</v>
+      </c>
+      <c r="G24">
+        <v>5400000</v>
+      </c>
+      <c r="H24">
+        <v>0</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>260000</v>
+      </c>
+      <c r="K24">
+        <v>2000000</v>
+      </c>
+      <c r="L24">
+        <v>450000</v>
+      </c>
+      <c r="M24">
+        <v>0</v>
+      </c>
+      <c r="N24">
+        <v>800000</v>
+      </c>
+      <c r="O24">
+        <v>1000000</v>
+      </c>
+      <c r="P24">
+        <v>0</v>
+      </c>
+      <c r="Q24">
+        <v>11195000</v>
+      </c>
+      <c r="R24">
+        <v>10600000</v>
+      </c>
+      <c r="S24">
+        <v>1360000</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>2049</v>
+      </c>
+      <c r="B25">
+        <v>7650000</v>
+      </c>
+      <c r="C25">
+        <v>2610000</v>
+      </c>
+      <c r="D25">
+        <v>112000</v>
+      </c>
+      <c r="E25">
+        <v>6290000</v>
+      </c>
+      <c r="F25">
+        <v>12950000</v>
+      </c>
+      <c r="G25">
+        <v>5400000</v>
+      </c>
+      <c r="H25">
+        <v>0</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>260000</v>
+      </c>
+      <c r="K25">
+        <v>2000000</v>
+      </c>
+      <c r="L25">
+        <v>450000</v>
+      </c>
+      <c r="M25">
+        <v>0</v>
+      </c>
+      <c r="N25">
+        <v>800000</v>
+      </c>
+      <c r="O25">
+        <v>1000000</v>
+      </c>
+      <c r="P25">
+        <v>0</v>
+      </c>
+      <c r="Q25">
+        <v>11195000</v>
+      </c>
+      <c r="R25">
+        <v>10600000</v>
+      </c>
+      <c r="S25">
+        <v>1360000</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>2050</v>
+      </c>
+      <c r="B26">
+        <v>7650000</v>
+      </c>
+      <c r="C26">
+        <v>2610000</v>
+      </c>
+      <c r="D26">
+        <v>112000</v>
+      </c>
+      <c r="E26">
+        <v>6290000</v>
+      </c>
+      <c r="F26">
+        <v>12950000</v>
+      </c>
+      <c r="G26">
+        <v>5400000</v>
+      </c>
+      <c r="H26">
+        <v>0</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>260000</v>
+      </c>
+      <c r="K26">
+        <v>2000000</v>
+      </c>
+      <c r="L26">
+        <v>450000</v>
+      </c>
+      <c r="M26">
+        <v>0</v>
+      </c>
+      <c r="N26">
+        <v>800000</v>
+      </c>
+      <c r="O26">
+        <v>1000000</v>
+      </c>
+      <c r="P26">
+        <v>0</v>
+      </c>
+      <c r="Q26">
+        <v>11195000</v>
+      </c>
+      <c r="R26">
+        <v>10600000</v>
+      </c>
+      <c r="S26">
+        <v>1360000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F3C079C-E0FE-4643-9E48-5AE3F12A3520}">
   <dimension ref="A1:E217"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -9925,7 +11497,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E6FE4EC-E3E7-42F5-A9DB-0136E2BCE431}">
   <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -10053,7 +11625,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7E57138-F43E-470A-BCDF-3CE08782F05D}">
   <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
